--- a/KER.PA.xlsx
+++ b/KER.PA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842FC56F-2BC3-4076-9EE3-4CD4E1CA4B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45082862-3B3F-405F-ABC4-94FC4A1C2969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{00BE0985-5336-41E3-B925-F565FA10FCAA}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{00BE0985-5336-41E3-B925-F565FA10FCAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="545">
   <si>
     <t>Kering</t>
   </si>
@@ -1825,6 +1825,9 @@
   </si>
   <si>
     <t>Debt Ratio</t>
+  </si>
+  <si>
+    <t>16-03-2026: launch of Kering Jewellery, CEO: Jean-Marc Duplaix</t>
   </si>
 </sst>
 </file>
@@ -1849,6 +1852,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2057,12 +2066,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial "/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -2318,27 +2321,27 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2349,41 +2352,41 @@
     <xf numFmtId="9" fontId="0" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="0" fillId="8" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="8" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="16" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2399,8 +2402,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2411,184 +2414,185 @@
     <xf numFmtId="167" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="23" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="29" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -2598,6 +2602,146 @@
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="84">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2655,6 +2799,246 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2770,346 +3154,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -3190,6 +3234,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3210,21 +3274,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3260,71 +3324,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3380,21 +3384,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7772,7 +7776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30076D03-558C-464F-8F0F-AA9F5CEE4D93}">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="58" customWidth="1"/>
@@ -7808,7 +7812,7 @@
       <c r="H3" s="62">
         <v>122.604812</v>
       </c>
-      <c r="I3" s="155" t="s">
+      <c r="I3" s="148" t="s">
         <v>513</v>
       </c>
       <c r="M3" s="61"/>
@@ -7837,7 +7841,7 @@
       <c r="H5" s="62">
         <v>4313</v>
       </c>
-      <c r="I5" s="155" t="s">
+      <c r="I5" s="148" t="s">
         <v>513</v>
       </c>
       <c r="N5" s="62"/>
@@ -7850,7 +7854,7 @@
         <f>10306+2046+170+40</f>
         <v>12562</v>
       </c>
-      <c r="I6" s="155" t="s">
+      <c r="I6" s="148" t="s">
         <v>513</v>
       </c>
       <c r="N6" s="62"/>
@@ -8195,8 +8199,13 @@
       </c>
     </row>
     <row r="58" spans="2:2">
-      <c r="B58" s="156" t="s">
+      <c r="B58" s="149" t="s">
         <v>542</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="157" t="s">
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -9496,7 +9505,7 @@
         <v>324</v>
       </c>
       <c r="H13" s="62">
-        <f t="shared" ref="H13:H18" si="12">+AB13</f>
+        <f t="shared" ref="H13:H17" si="12">+AB13</f>
         <v>308</v>
       </c>
       <c r="I13" s="62"/>
@@ -10740,7 +10749,7 @@
         <v>1349</v>
       </c>
       <c r="AC24" s="62">
-        <f t="shared" ref="AB24:AF24" si="25">8%*AC44</f>
+        <f t="shared" ref="AC24:AF24" si="25">8%*AC44</f>
         <v>1273.4175700934577</v>
       </c>
       <c r="AD24" s="62">
@@ -11074,7 +11083,7 @@
         <v>3522</v>
       </c>
       <c r="AC27" s="62">
-        <f t="shared" ref="AB27:AF27" si="29">+AC44-AC26</f>
+        <f t="shared" ref="AC27:AF27" si="29">+AC44-AC26</f>
         <v>3183.5439252336437</v>
       </c>
       <c r="AD27" s="62">
@@ -11960,7 +11969,7 @@
         <v>4.9399326599326603</v>
       </c>
       <c r="AC34" s="79">
-        <f t="shared" ref="AB34:AF34" si="37">0.82*AC40/AC33</f>
+        <f t="shared" ref="AC34:AF34" si="37">0.82*AC40/AC33</f>
         <v>2.768718504672897</v>
       </c>
       <c r="AD34" s="79">
@@ -12231,7 +12240,7 @@
         <v>3.6427406199021206</v>
       </c>
       <c r="AC36" s="79">
-        <f t="shared" ref="AB36:AF36" si="39">0.72*AC41/AC35</f>
+        <f t="shared" ref="AC36:AF36" si="39">0.72*AC41/AC35</f>
         <v>3.3708112149532705</v>
       </c>
       <c r="AD36" s="79">
@@ -43257,14 +43266,14 @@
       </c>
       <c r="E4" s="48">
         <f ca="1">+TODAY()</f>
-        <v>46065</v>
+        <v>46098</v>
       </c>
       <c r="G4" t="s">
         <v>152</v>
       </c>
       <c r="J4" s="56">
         <f ca="1">V62</f>
-        <v>351.39459163127577</v>
+        <v>348.81536470668891</v>
       </c>
       <c r="L4" t="s">
         <v>534</v>
@@ -43286,7 +43295,7 @@
       </c>
       <c r="J5" s="16">
         <f ca="1">J4/J3-1</f>
-        <v>0.23382932454801875</v>
+        <v>0.2247730502341605</v>
       </c>
       <c r="L5" t="s">
         <v>154</v>
@@ -44905,43 +44914,43 @@
       <c r="L52" s="44"/>
       <c r="M52" s="44">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>135.59649439933011</v>
+        <v>246.51946086172541</v>
       </c>
       <c r="N52" s="44">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>1402.3604734755204</v>
+        <v>1390.6600383589825</v>
       </c>
       <c r="O52" s="44">
         <f t="shared" ref="O52:U52" ca="1" si="23">O51/(1+$E$18)^O53</f>
-        <v>1776.4971721433342</v>
+        <v>1761.6751700329482</v>
       </c>
       <c r="P52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2128.4392997280052</v>
+        <v>2110.6809085033606</v>
       </c>
       <c r="Q52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2674.7043518026717</v>
+        <v>2652.3882602441095</v>
       </c>
       <c r="R52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2792.8898931828048</v>
+        <v>2769.5877340012698</v>
       </c>
       <c r="S52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2894.9076654343071</v>
+        <v>2870.7543325727243</v>
       </c>
       <c r="T52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2851.0160693491275</v>
+        <v>2827.2289410275821</v>
       </c>
       <c r="U52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2650.7354277728891</v>
+        <v>2628.6193182059246</v>
       </c>
       <c r="V52" s="45">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>2461.4709231567058</v>
+        <v>2440.9339204584899</v>
       </c>
     </row>
     <row r="53" spans="2:24">
@@ -44950,43 +44959,43 @@
       </c>
       <c r="M53" s="53">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.11666666666666667</v>
+        <v>0.21388888888888888</v>
       </c>
       <c r="N53" s="53">
         <f ca="1">M53+1</f>
-        <v>1.1166666666666667</v>
+        <v>1.2138888888888888</v>
       </c>
       <c r="O53" s="53">
         <f ca="1">N53+1</f>
-        <v>2.1166666666666667</v>
+        <v>2.2138888888888886</v>
       </c>
       <c r="P53" s="53">
         <f t="shared" ref="P53:V53" ca="1" si="24">O53+1</f>
-        <v>3.1166666666666667</v>
+        <v>3.2138888888888886</v>
       </c>
       <c r="Q53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>4.1166666666666671</v>
+        <v>4.2138888888888886</v>
       </c>
       <c r="R53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>5.1166666666666671</v>
+        <v>5.2138888888888886</v>
       </c>
       <c r="S53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>6.1166666666666671</v>
+        <v>6.2138888888888886</v>
       </c>
       <c r="T53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>7.1166666666666671</v>
+        <v>7.2138888888888886</v>
       </c>
       <c r="U53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>8.1166666666666671</v>
+        <v>8.2138888888888886</v>
       </c>
       <c r="V53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>9.1166666666666671</v>
+        <v>9.2138888888888886</v>
       </c>
     </row>
     <row r="54" spans="2:24">
@@ -44999,7 +45008,7 @@
       <c r="Q54" s="4"/>
       <c r="V54" s="8">
         <f ca="1">SUM(M52:V52)</f>
-        <v>21768.617770444696</v>
+        <v>21699.048084267117</v>
       </c>
     </row>
     <row r="55" spans="2:24">
@@ -45041,7 +45050,7 @@
       <c r="U56" s="9"/>
       <c r="V56" s="50">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>29563.050074324645</v>
+        <v>29316.394128307908</v>
       </c>
     </row>
     <row r="57" spans="2:24">
@@ -45069,7 +45078,7 @@
       <c r="U57" s="34"/>
       <c r="V57" s="55">
         <f ca="1">V54+V56</f>
-        <v>51331.667844769341</v>
+        <v>51015.442212575028</v>
       </c>
     </row>
     <row r="58" spans="2:24">
@@ -45123,7 +45132,7 @@
       <c r="Q60" s="4"/>
       <c r="V60" s="46">
         <f ca="1">V57+V58-V59</f>
-        <v>43082.667844769341</v>
+        <v>42766.442212575028</v>
       </c>
     </row>
     <row r="61" spans="2:24">
@@ -45160,7 +45169,7 @@
       </c>
       <c r="V62" s="46">
         <f ca="1">V60/V61</f>
-        <v>351.39459163127577</v>
+        <v>348.81536470668891</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -45193,35 +45202,35 @@
     </row>
     <row r="68" spans="1:22">
       <c r="B68" s="35"/>
-      <c r="C68" s="148" t="s">
+      <c r="C68" s="150" t="s">
         <v>165</v>
       </c>
-      <c r="D68" s="148"/>
-      <c r="E68" s="148"/>
-      <c r="F68" s="148"/>
-      <c r="G68" s="148"/>
-      <c r="H68" s="148"/>
-      <c r="I68" s="148"/>
-      <c r="J68" s="149"/>
+      <c r="D68" s="150"/>
+      <c r="E68" s="150"/>
+      <c r="F68" s="150"/>
+      <c r="G68" s="150"/>
+      <c r="H68" s="150"/>
+      <c r="I68" s="150"/>
+      <c r="J68" s="151"/>
       <c r="M68" s="35"/>
-      <c r="N68" s="152" t="s">
+      <c r="N68" s="154" t="s">
         <v>537</v>
       </c>
-      <c r="O68" s="152"/>
-      <c r="P68" s="152"/>
-      <c r="Q68" s="152"/>
-      <c r="R68" s="152"/>
-      <c r="S68" s="152"/>
-      <c r="T68" s="152"/>
-      <c r="U68" s="153"/>
+      <c r="O68" s="154"/>
+      <c r="P68" s="154"/>
+      <c r="Q68" s="154"/>
+      <c r="R68" s="154"/>
+      <c r="S68" s="154"/>
+      <c r="T68" s="154"/>
+      <c r="U68" s="155"/>
     </row>
     <row r="69" spans="1:22" ht="15" customHeight="1">
-      <c r="B69" s="150" t="s">
+      <c r="B69" s="152" t="s">
         <v>164</v>
       </c>
       <c r="C69" s="36">
         <f ca="1">+J4</f>
-        <v>351.39459163127577</v>
+        <v>348.81536470668891</v>
       </c>
       <c r="D69" s="51">
         <v>5.0000000000000001E-3</v>
@@ -45244,12 +45253,12 @@
       <c r="J69" s="51">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="M69" s="150" t="s">
+      <c r="M69" s="152" t="s">
         <v>164</v>
       </c>
       <c r="N69" s="36">
         <f ca="1">+J4</f>
-        <v>351.39459163127577</v>
+        <v>348.81536470668891</v>
       </c>
       <c r="O69" s="51">
         <v>7.0000000000000007E-2</v>
@@ -45274,369 +45283,369 @@
       </c>
     </row>
     <row r="70" spans="1:22">
-      <c r="B70" s="150"/>
+      <c r="B70" s="152"/>
       <c r="C70" s="37">
         <v>0.06</v>
       </c>
       <c r="D70" s="38">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>603.16718684412285</v>
+        <v>600.29923167731761</v>
       </c>
       <c r="E70" s="38">
-        <v>625.06720311867139</v>
+        <v>622.07553439432354</v>
       </c>
       <c r="F70" s="38">
-        <v>651.53747011324367</v>
+        <v>648.39627040873825</v>
       </c>
       <c r="G70" s="52">
-        <v>684.29183184784904</v>
+        <v>680.96560220709034</v>
       </c>
       <c r="H70" s="38">
-        <v>726.02347178250113</v>
+        <v>722.46149941106648</v>
       </c>
       <c r="I70" s="38">
-        <v>781.22102901722394</v>
+        <v>777.34724472348012</v>
       </c>
       <c r="J70" s="38">
-        <v>857.96405393205919</v>
-      </c>
-      <c r="M70" s="150"/>
+        <v>853.65674700939235</v>
+      </c>
+      <c r="M70" s="152"/>
       <c r="N70" s="37">
         <v>0.06</v>
       </c>
       <c r="O70" s="38">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>625.98186919943089</v>
+        <v>622.98503351112299</v>
       </c>
       <c r="P70" s="38">
-        <v>650.27768696960504</v>
+        <v>647.14360380110941</v>
       </c>
       <c r="Q70" s="38">
-        <v>669.17443412418504</v>
+        <v>665.93360291554313</v>
       </c>
       <c r="R70" s="52">
-        <v>684.29183184784904</v>
+        <v>680.96560220709034</v>
       </c>
       <c r="S70" s="38">
-        <v>696.66061180357428</v>
+        <v>693.26451071835595</v>
       </c>
       <c r="T70" s="38">
-        <v>706.96792843334515</v>
+        <v>703.51360114441081</v>
       </c>
       <c r="U70" s="38">
-        <v>715.68950404315115</v>
+        <v>712.18590842799551</v>
       </c>
     </row>
     <row r="71" spans="1:22">
-      <c r="B71" s="150"/>
+      <c r="B71" s="152"/>
       <c r="C71" s="37">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="38">
-        <v>489.12814528370228</v>
+        <v>486.39771240361659</v>
       </c>
       <c r="E71" s="38">
-        <v>500.43079587973074</v>
+        <v>497.62625901364999</v>
       </c>
       <c r="F71" s="38">
-        <v>513.56584589057002</v>
+        <v>510.67519121046149</v>
       </c>
       <c r="G71" s="52">
-        <v>529.08301514066306</v>
+        <v>526.09062467008471</v>
       </c>
       <c r="H71" s="38">
-        <v>547.77634337642792</v>
+        <v>544.66139314678969</v>
       </c>
       <c r="I71" s="38">
-        <v>570.8368902174916</v>
+        <v>567.57074727198278</v>
       </c>
       <c r="J71" s="38">
-        <v>600.13632078041087</v>
-      </c>
-      <c r="M71" s="150"/>
+        <v>596.6780808950158</v>
+      </c>
+      <c r="M71" s="152"/>
       <c r="N71" s="37">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="38">
-        <v>486.26211602542367</v>
+        <v>483.55047379892966</v>
       </c>
       <c r="P71" s="38">
-        <v>504.10415732344001</v>
+        <v>501.27553666191085</v>
       </c>
       <c r="Q71" s="38">
-        <v>517.98130055523063</v>
+        <v>515.06169666645189</v>
       </c>
       <c r="R71" s="52">
-        <v>529.08301514066306</v>
+        <v>526.09062467008471</v>
       </c>
       <c r="S71" s="38">
-        <v>538.16623616510788</v>
+        <v>535.11429303669331</v>
       </c>
       <c r="T71" s="38">
-        <v>545.73558701881177</v>
+        <v>542.63401667553387</v>
       </c>
       <c r="U71" s="38">
-        <v>552.14042235656132</v>
+        <v>548.9968597545527</v>
       </c>
     </row>
     <row r="72" spans="1:22">
-      <c r="B72" s="150"/>
+      <c r="B72" s="152"/>
       <c r="C72" s="37">
         <v>0.08</v>
       </c>
       <c r="D72" s="52">
-        <v>405.90713817907084</v>
+        <v>403.29555318315931</v>
       </c>
       <c r="E72" s="52">
-        <v>411.66016321777562</v>
+        <v>409.00569286886383</v>
       </c>
       <c r="F72" s="52">
-        <v>418.1252085448977</v>
+        <v>415.42254515855763</v>
       </c>
       <c r="G72" s="52">
-        <v>425.48027923254136</v>
+        <v>422.72278820323783</v>
       </c>
       <c r="H72" s="52">
-        <v>433.9681094699398</v>
+        <v>431.14734675426445</v>
       </c>
       <c r="I72" s="52">
-        <v>443.92852712201926</v>
+        <v>441.03351546354168</v>
       </c>
       <c r="J72" s="52">
-        <v>455.85239466034051</v>
-      </c>
-      <c r="M72" s="150"/>
+        <v>452.86849771715265</v>
+      </c>
+      <c r="M72" s="152"/>
       <c r="N72" s="37">
         <v>0.08</v>
       </c>
       <c r="O72" s="52">
-        <v>392.69767845332973</v>
+        <v>390.18456206123454</v>
       </c>
       <c r="P72" s="52">
-        <v>406.35709544466789</v>
+        <v>403.74215628706924</v>
       </c>
       <c r="Q72" s="52">
-        <v>416.98108643793103</v>
+        <v>414.28695179605182</v>
       </c>
       <c r="R72" s="52">
-        <v>425.48027923254136</v>
+        <v>422.72278820323783</v>
       </c>
       <c r="S72" s="52">
-        <v>432.43416424631351</v>
+        <v>429.6248361727537</v>
       </c>
       <c r="T72" s="52">
-        <v>438.22906842445701</v>
+        <v>435.37654281401694</v>
       </c>
       <c r="U72" s="52">
-        <v>443.13244888288614</v>
+        <v>440.24337151047041</v>
       </c>
     </row>
     <row r="73" spans="1:22">
-      <c r="B73" s="150"/>
+      <c r="B73" s="152"/>
       <c r="C73" s="37">
         <v>0.09</v>
       </c>
       <c r="D73" s="38">
-        <v>342.60793200820507</v>
+        <v>340.10201557885489</v>
       </c>
       <c r="E73" s="38">
-        <v>345.29998721913097</v>
+        <v>342.7716099333025</v>
       </c>
       <c r="F73" s="38">
-        <v>348.21308500481473</v>
+        <v>345.66040261892516</v>
       </c>
       <c r="G73" s="52">
-        <v>351.39459163127577</v>
+        <v>348.81536470668891</v>
       </c>
       <c r="H73" s="38">
-        <v>354.9064476002319</v>
+        <v>352.29791990478003</v>
       </c>
       <c r="I73" s="38">
-        <v>358.83124024730694</v>
+        <v>356.18996649078048</v>
       </c>
       <c r="J73" s="38">
-        <v>363.2815886665332</v>
-      </c>
-      <c r="M73" s="150"/>
+        <v>360.60318393412007</v>
+      </c>
+      <c r="M73" s="152"/>
       <c r="N73" s="37">
         <v>0.09</v>
       </c>
       <c r="O73" s="38">
-        <v>325.55980098031426</v>
+        <v>323.19612369326933</v>
       </c>
       <c r="P73" s="38">
-        <v>336.32429708488161</v>
+        <v>333.87080744886083</v>
       </c>
       <c r="Q73" s="38">
-        <v>344.69668294398946</v>
+        <v>342.17333925876534</v>
       </c>
       <c r="R73" s="52">
-        <v>351.39459163127577</v>
+        <v>348.81536470668891</v>
       </c>
       <c r="S73" s="38">
-        <v>356.87469873905553</v>
+        <v>354.24974916408092</v>
       </c>
       <c r="T73" s="38">
-        <v>361.44145466220533</v>
+        <v>358.7784028785743</v>
       </c>
       <c r="U73" s="38">
-        <v>365.30563275102429</v>
+        <v>362.61034063699168</v>
       </c>
     </row>
     <row r="74" spans="1:22">
-      <c r="B74" s="150"/>
+      <c r="B74" s="152"/>
       <c r="C74" s="37">
         <v>0.1</v>
       </c>
       <c r="D74" s="38">
-        <v>292.92324670483174</v>
+        <v>290.5130759585993</v>
       </c>
       <c r="E74" s="38">
-        <v>293.87486153611093</v>
+        <v>291.45591360100627</v>
       </c>
       <c r="F74" s="38">
-        <v>294.82647636739006</v>
+        <v>292.3987512434133</v>
       </c>
       <c r="G74" s="52">
-        <v>295.7780911986693</v>
+        <v>293.34158888582039</v>
       </c>
       <c r="H74" s="38">
-        <v>296.72970602994837</v>
+        <v>294.28442652822724</v>
       </c>
       <c r="I74" s="38">
-        <v>297.68132086122756</v>
+        <v>295.22726417063427</v>
       </c>
       <c r="J74" s="38">
-        <v>298.63293569250675</v>
-      </c>
-      <c r="M74" s="150"/>
+        <v>296.1701018130413</v>
+      </c>
+      <c r="M74" s="152"/>
       <c r="N74" s="37">
         <v>0.1</v>
       </c>
       <c r="O74" s="38">
-        <v>274.9785098864246</v>
+        <v>272.73385184463882</v>
       </c>
       <c r="P74" s="38">
-        <v>283.64500209985988</v>
+        <v>281.32040894513108</v>
       </c>
       <c r="Q74" s="38">
-        <v>290.38560715475393</v>
+        <v>287.99884224551403</v>
       </c>
       <c r="R74" s="52">
-        <v>295.7780911986693</v>
+        <v>293.34158888582039</v>
       </c>
       <c r="S74" s="38">
-        <v>300.19012359823637</v>
+        <v>297.71292704607089</v>
       </c>
       <c r="T74" s="38">
-        <v>303.86681726454219</v>
+        <v>301.35570884627981</v>
       </c>
       <c r="U74" s="38">
-        <v>306.9778657514164</v>
+        <v>304.43806267722573</v>
       </c>
     </row>
     <row r="75" spans="1:22">
-      <c r="B75" s="150"/>
+      <c r="B75" s="152"/>
       <c r="C75" s="37">
         <v>0.11</v>
       </c>
       <c r="D75" s="38">
-        <v>252.94947475101014</v>
+        <v>250.62720498760166</v>
       </c>
       <c r="E75" s="38">
-        <v>252.89940309252225</v>
+        <v>250.57763879321493</v>
       </c>
       <c r="F75" s="38">
-        <v>252.75182346750535</v>
+        <v>250.4315489571276</v>
       </c>
       <c r="G75" s="52">
-        <v>252.49048454820468</v>
+        <v>250.17284820572306</v>
       </c>
       <c r="H75" s="38">
-        <v>252.09531116504061</v>
+        <v>249.78166402453334</v>
       </c>
       <c r="I75" s="38">
-        <v>251.54120935603876</v>
+        <v>249.23315577047399</v>
       </c>
       <c r="J75" s="38">
-        <v>250.79639343603165</v>
-      </c>
-      <c r="M75" s="150"/>
+        <v>248.49585862897089</v>
+      </c>
+      <c r="M75" s="152"/>
       <c r="N75" s="37">
         <v>0.11</v>
       </c>
       <c r="O75" s="38">
-        <v>235.46612066232854</v>
+        <v>233.32034211422379</v>
       </c>
       <c r="P75" s="38">
-        <v>242.5596056147769</v>
+        <v>240.34221965234846</v>
       </c>
       <c r="Q75" s="38">
-        <v>248.07676057779236</v>
+        <v>245.8036799597788</v>
       </c>
       <c r="R75" s="52">
-        <v>252.49048454820468</v>
+        <v>250.17284820572306</v>
       </c>
       <c r="S75" s="38">
-        <v>256.1017132512693</v>
+        <v>253.74762222513192</v>
       </c>
       <c r="T75" s="38">
-        <v>259.11107050382316</v>
+        <v>256.72660057463941</v>
       </c>
       <c r="U75" s="38">
-        <v>261.65744971752258</v>
+        <v>259.2472745626842</v>
       </c>
     </row>
     <row r="76" spans="1:22">
-      <c r="B76" s="151"/>
+      <c r="B76" s="153"/>
       <c r="C76" s="37">
         <v>0.12</v>
       </c>
       <c r="D76" s="38">
-        <v>220.14155095674599</v>
+        <v>217.90074500540914</v>
       </c>
       <c r="E76" s="38">
-        <v>219.51920152319593</v>
+        <v>217.28521502181749</v>
       </c>
       <c r="F76" s="38">
-        <v>218.76067990589479</v>
+        <v>216.53500497344007</v>
       </c>
       <c r="G76" s="52">
-        <v>217.84556027727979</v>
+        <v>215.62991285055892</v>
       </c>
       <c r="H76" s="38">
-        <v>216.74911663556463</v>
+        <v>214.54548358877869</v>
       </c>
       <c r="I76" s="38">
-        <v>215.44112831189932</v>
+        <v>213.25182766494962</v>
       </c>
       <c r="J76" s="38">
-        <v>213.88426389182194</v>
-      </c>
-      <c r="M76" s="151"/>
+        <v>211.71202272694529</v>
+      </c>
+      <c r="M76" s="153"/>
       <c r="N76" s="37">
         <v>0.12</v>
       </c>
       <c r="O76" s="38">
-        <v>203.72657172150605</v>
+        <v>201.66563438324948</v>
       </c>
       <c r="P76" s="38">
-        <v>209.60948361974511</v>
+        <v>207.48408374462844</v>
       </c>
       <c r="Q76" s="38">
-        <v>214.18508176281995</v>
+        <v>212.00954435903427</v>
       </c>
       <c r="R76" s="52">
-        <v>217.84556027727979</v>
+        <v>215.62991285055892</v>
       </c>
       <c r="S76" s="38">
-        <v>220.8404972436561</v>
+        <v>218.59203252544273</v>
       </c>
       <c r="T76" s="38">
-        <v>223.3362780489696</v>
+        <v>221.06046558784595</v>
       </c>
       <c r="U76" s="38">
-        <v>225.44809257654259</v>
+        <v>223.14913971757173</v>
       </c>
     </row>
   </sheetData>
@@ -47965,23 +47974,23 @@
     <row r="3" spans="1:35">
       <c r="A3" s="92"/>
       <c r="B3" s="91"/>
-      <c r="C3" s="154" t="s">
+      <c r="C3" s="156" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="154"/>
-      <c r="E3" s="154"/>
-      <c r="F3" s="154"/>
-      <c r="G3" s="154"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="154" t="s">
+      <c r="D3" s="156"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="156"/>
+      <c r="H3" s="156"/>
+      <c r="I3" s="156"/>
+      <c r="J3" s="156" t="s">
         <v>118</v>
       </c>
-      <c r="K3" s="154"/>
-      <c r="L3" s="154"/>
-      <c r="M3" s="154"/>
-      <c r="N3" s="154"/>
-      <c r="O3" s="154"/>
+      <c r="K3" s="156"/>
+      <c r="L3" s="156"/>
+      <c r="M3" s="156"/>
+      <c r="N3" s="156"/>
+      <c r="O3" s="156"/>
       <c r="P3" s="91"/>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>
@@ -51825,8 +51834,8 @@
     <mergeCell ref="J3:O3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J20">
-    <cfRule type="top10" dxfId="79" priority="69" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="78" priority="79" rank="5"/>
+    <cfRule type="top10" dxfId="79" priority="79" rank="5"/>
+    <cfRule type="top10" dxfId="78" priority="69" bottom="1" rank="5"/>
     <cfRule type="top10" dxfId="77" priority="80" percent="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9">
@@ -51842,40 +51851,40 @@
     <cfRule type="top10" dxfId="73" priority="63" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K7:K10 K19:K20 K17 K12:K14">
-    <cfRule type="top10" dxfId="72" priority="68" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="71" priority="78" rank="5"/>
+    <cfRule type="top10" dxfId="72" priority="78" rank="5"/>
+    <cfRule type="top10" dxfId="71" priority="68" bottom="1" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="top10" dxfId="70" priority="43" rank="10"/>
-    <cfRule type="top10" dxfId="69" priority="44" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="68" priority="45" rank="5"/>
-    <cfRule type="top10" dxfId="67" priority="46" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="70" priority="46" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="69" priority="45" rank="5"/>
+    <cfRule type="top10" dxfId="68" priority="44" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="67" priority="43" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K15:K16">
-    <cfRule type="top10" dxfId="66" priority="47" rank="10"/>
-    <cfRule type="top10" dxfId="65" priority="48" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="64" priority="49" rank="5"/>
-    <cfRule type="top10" dxfId="63" priority="50" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="66" priority="50" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="65" priority="49" rank="5"/>
+    <cfRule type="top10" dxfId="64" priority="48" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="63" priority="47" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:L6">
     <cfRule type="top10" dxfId="62" priority="39" rank="10"/>
     <cfRule type="top10" dxfId="61" priority="40" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="60" priority="41" rank="5"/>
-    <cfRule type="top10" dxfId="59" priority="42" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="60" priority="42" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="59" priority="41" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K18:N18">
-    <cfRule type="top10" dxfId="58" priority="59" rank="10"/>
-    <cfRule type="top10" dxfId="57" priority="60" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="58" priority="60" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="57" priority="62" percent="1" rank="10"/>
     <cfRule type="top10" dxfId="56" priority="61" rank="5"/>
-    <cfRule type="top10" dxfId="55" priority="62" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="55" priority="59" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:L8 L10:L12 L14:L17 L19:L20">
-    <cfRule type="cellIs" dxfId="54" priority="67" operator="between">
+    <cfRule type="cellIs" dxfId="54" priority="77" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="53" priority="67" operator="between">
       <formula>0</formula>
       <formula>1.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="53" priority="77" operator="lessThan">
-      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:L8 L19:L20 L10:L12 L14:L17">
@@ -51894,19 +51903,19 @@
     <cfRule type="top10" dxfId="44" priority="34" percent="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:M10 M20 M15:M17 M12:M13">
-    <cfRule type="top10" dxfId="43" priority="70" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="42" priority="75" rank="5"/>
+    <cfRule type="top10" dxfId="43" priority="75" rank="5"/>
+    <cfRule type="top10" dxfId="42" priority="70" bottom="1" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11">
-    <cfRule type="top10" dxfId="41" priority="23" rank="10"/>
+    <cfRule type="top10" dxfId="41" priority="25" rank="5"/>
     <cfRule type="top10" dxfId="40" priority="24" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="39" priority="25" rank="5"/>
+    <cfRule type="top10" dxfId="39" priority="23" rank="10"/>
     <cfRule type="top10" dxfId="38" priority="26" percent="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M14">
-    <cfRule type="top10" dxfId="37" priority="27" rank="10"/>
+    <cfRule type="top10" dxfId="37" priority="29" rank="5"/>
     <cfRule type="top10" dxfId="36" priority="28" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="35" priority="29" rank="5"/>
+    <cfRule type="top10" dxfId="35" priority="27" rank="10"/>
     <cfRule type="top10" dxfId="34" priority="30" percent="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="M19">
@@ -51920,16 +51929,16 @@
     <cfRule type="top10" dxfId="28" priority="74" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N9">
-    <cfRule type="top10" dxfId="27" priority="19" rank="10"/>
-    <cfRule type="top10" dxfId="26" priority="20" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="25" priority="21" rank="5"/>
-    <cfRule type="top10" dxfId="24" priority="22" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="27" priority="21" rank="5"/>
+    <cfRule type="top10" dxfId="26" priority="22" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="25" priority="20" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="24" priority="19" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16">
-    <cfRule type="top10" dxfId="23" priority="15" rank="10"/>
-    <cfRule type="top10" dxfId="22" priority="16" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="21" priority="17" rank="5"/>
-    <cfRule type="top10" dxfId="20" priority="18" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="23" priority="18" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="22" priority="17" rank="5"/>
+    <cfRule type="top10" dxfId="21" priority="15" rank="10"/>
+    <cfRule type="top10" dxfId="20" priority="16" bottom="1" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N12:O12">
     <cfRule type="top10" dxfId="19" priority="11" rank="10"/>
@@ -51942,22 +51951,22 @@
     <cfRule type="top10" dxfId="14" priority="73" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10">
-    <cfRule type="top10" dxfId="13" priority="1" rank="10"/>
-    <cfRule type="top10" dxfId="12" priority="2" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="11" priority="3" rank="5"/>
-    <cfRule type="top10" dxfId="10" priority="4" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="13" priority="2" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="12" priority="3" rank="5"/>
+    <cfRule type="top10" dxfId="11" priority="4" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="10" priority="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O19">
-    <cfRule type="top10" dxfId="9" priority="51" rank="10"/>
-    <cfRule type="top10" dxfId="8" priority="52" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="9" priority="52" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="8" priority="51" rank="10"/>
     <cfRule type="top10" dxfId="7" priority="53" rank="5"/>
     <cfRule type="top10" dxfId="6" priority="54" percent="1" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O6:P6">
-    <cfRule type="top10" dxfId="5" priority="7" rank="10"/>
-    <cfRule type="top10" dxfId="4" priority="8" bottom="1" rank="5"/>
-    <cfRule type="top10" dxfId="3" priority="9" rank="5"/>
-    <cfRule type="top10" dxfId="2" priority="10" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="5" priority="10" percent="1" rank="10"/>
+    <cfRule type="top10" dxfId="4" priority="9" rank="5"/>
+    <cfRule type="top10" dxfId="3" priority="8" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="2" priority="7" rank="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P12">
     <cfRule type="top10" dxfId="1" priority="5" bottom="1" rank="5"/>

--- a/KER.PA.xlsx
+++ b/KER.PA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45082862-3B3F-405F-ABC4-94FC4A1C2969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BE5EE3-8D4A-4F83-84DE-AD489149F947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{00BE0985-5336-41E3-B925-F565FA10FCAA}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{00BE0985-5336-41E3-B925-F565FA10FCAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="548">
   <si>
     <t>Kering</t>
   </si>
@@ -1828,6 +1828,15 @@
   </si>
   <si>
     <t>16-03-2026: launch of Kering Jewellery, CEO: Jean-Marc Duplaix</t>
+  </si>
+  <si>
+    <t>Latest drop: Primavera</t>
+  </si>
+  <si>
+    <t>https://www.businessoffashion.com/articles/luxury/gucci-demna-pricing-strategy/?utm_source=newsletter_daily_digest&amp;utm_medium=email&amp;utm_campaign=Daily_Digest_180326&amp;cid=587aba24-4127-469f-8d2d-6bf7a31b470b&amp;did=69ba3f805900d1b23aaac8f231f99758&amp;uid=2360165579082&amp;utm_content=intro</t>
+  </si>
+  <si>
+    <t>created surge in Website traffic: jumped to 316.000 (average 180-210.000) visitors per day</t>
   </si>
 </sst>
 </file>
@@ -1845,13 +1854,19 @@
     <numFmt numFmtId="171" formatCode="#,##0.00;\(#,##0.00\)"/>
     <numFmt numFmtId="172" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2321,27 +2336,27 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2352,41 +2367,41 @@
     <xf numFmtId="9" fontId="0" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="0" fillId="8" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="8" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="16" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="17" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="165" fontId="7" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2402,8 +2417,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2414,184 +2429,185 @@
     <xf numFmtId="167" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="23" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="23" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="24" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="24" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="33" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="30" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6874,6 +6890,67 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>452438</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>11906</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>382921</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>59531</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="A snapshot of Gucci's pricing, following its Primavera drop.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC3F261A-3CF6-9639-05AF-AA1F306C33F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="11691938" y="1035844"/>
+          <a:ext cx="1752139" cy="2714625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8204,7 +8281,7 @@
       </c>
     </row>
     <row r="59" spans="2:2">
-      <c r="B59" s="157" t="s">
+      <c r="B59" s="150" t="s">
         <v>544</v>
       </c>
     </row>
@@ -8220,25 +8297,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78D5ED4-7405-435A-A1C5-535959068216}">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="58" bestFit="1" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="58"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:21">
       <c r="A1" s="63" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:21">
       <c r="A2" s="63"/>
       <c r="B2" s="57" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:21" ht="15">
       <c r="A3" s="63"/>
       <c r="B3" s="58" t="s">
         <v>519</v>
@@ -8246,14 +8323,21 @@
       <c r="D3" s="58" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="U3"/>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="63"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="T4" s="158" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="63"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="T5" s="58" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="B7" s="57" t="s">
         <v>315</v>
       </c>
@@ -8261,7 +8345,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:21">
       <c r="B8" s="89" t="s">
         <v>541</v>
       </c>
@@ -8269,7 +8353,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:21">
       <c r="B9" s="58" t="s">
         <v>431</v>
       </c>
@@ -8277,7 +8361,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:21">
       <c r="B10" s="58" t="s">
         <v>506</v>
       </c>
@@ -8285,7 +8369,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:21">
       <c r="B11" s="58" t="s">
         <v>363</v>
       </c>
@@ -8293,7 +8377,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:21">
       <c r="B12" s="58" t="s">
         <v>364</v>
       </c>
@@ -8301,63 +8385,66 @@
         <v>406</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:21">
       <c r="B14" s="61" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:21">
       <c r="B15" s="58" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:21">
       <c r="B16" s="76"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:20">
       <c r="B17" s="58" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:20">
       <c r="B18" s="58" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:20">
       <c r="B20" s="58" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:20">
       <c r="B21" s="58" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:20">
       <c r="B22" s="58" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:20">
       <c r="B24" s="58" t="s">
         <v>399</v>
       </c>
       <c r="D24" s="58" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="25" spans="2:10">
+      <c r="T24" s="158" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20">
       <c r="B25" s="58" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:20">
       <c r="B27" s="57" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:20">
       <c r="B28" s="58" t="s">
         <v>500</v>
       </c>
@@ -8368,7 +8455,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:20">
       <c r="B29" s="58" t="s">
         <v>391</v>
       </c>
@@ -8376,7 +8463,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:20">
       <c r="B30" s="58" t="s">
         <v>368</v>
       </c>
@@ -8384,7 +8471,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:20">
       <c r="B31" s="58" t="s">
         <v>369</v>
       </c>
@@ -43266,14 +43353,14 @@
       </c>
       <c r="E4" s="48">
         <f ca="1">+TODAY()</f>
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="G4" t="s">
         <v>152</v>
       </c>
       <c r="J4" s="56">
         <f ca="1">V62</f>
-        <v>348.81536470668891</v>
+        <v>348.74187691528448</v>
       </c>
       <c r="L4" t="s">
         <v>534</v>
@@ -43295,7 +43382,7 @@
       </c>
       <c r="J5" s="16">
         <f ca="1">J4/J3-1</f>
-        <v>0.2247730502341605</v>
+        <v>0.22451501725872358</v>
       </c>
       <c r="L5" t="s">
         <v>154</v>
@@ -44914,43 +45001,43 @@
       <c r="L52" s="44"/>
       <c r="M52" s="44">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>246.51946086172541</v>
+        <v>249.66124061830087</v>
       </c>
       <c r="N52" s="44">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>1390.6600383589825</v>
+        <v>1390.3271785388665</v>
       </c>
       <c r="O52" s="44">
         <f t="shared" ref="O52:U52" ca="1" si="23">O51/(1+$E$18)^O53</f>
-        <v>1761.6751700329482</v>
+        <v>1761.253506316421</v>
       </c>
       <c r="P52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2110.6809085033606</v>
+        <v>2110.1757089231983</v>
       </c>
       <c r="Q52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2652.3882602441095</v>
+        <v>2651.7534009292303</v>
       </c>
       <c r="R52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2769.5877340012698</v>
+        <v>2768.9248225423171</v>
       </c>
       <c r="S52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2870.7543325727243</v>
+        <v>2870.067206499938</v>
       </c>
       <c r="T52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2827.2289410275821</v>
+        <v>2826.5522329243936</v>
       </c>
       <c r="U52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2628.6193182059246</v>
+        <v>2627.9901480785911</v>
       </c>
       <c r="V52" s="45">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>2440.9339204584899</v>
+        <v>2440.3496735517915</v>
       </c>
     </row>
     <row r="53" spans="2:24">
@@ -44959,43 +45046,43 @@
       </c>
       <c r="M53" s="53">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.21388888888888888</v>
+        <v>0.21666666666666667</v>
       </c>
       <c r="N53" s="53">
         <f ca="1">M53+1</f>
-        <v>1.2138888888888888</v>
+        <v>1.2166666666666668</v>
       </c>
       <c r="O53" s="53">
         <f ca="1">N53+1</f>
-        <v>2.2138888888888886</v>
+        <v>2.2166666666666668</v>
       </c>
       <c r="P53" s="53">
         <f t="shared" ref="P53:V53" ca="1" si="24">O53+1</f>
-        <v>3.2138888888888886</v>
+        <v>3.2166666666666668</v>
       </c>
       <c r="Q53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>4.2138888888888886</v>
+        <v>4.2166666666666668</v>
       </c>
       <c r="R53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>5.2138888888888886</v>
+        <v>5.2166666666666668</v>
       </c>
       <c r="S53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>6.2138888888888886</v>
+        <v>6.2166666666666668</v>
       </c>
       <c r="T53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>7.2138888888888886</v>
+        <v>7.2166666666666668</v>
       </c>
       <c r="U53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>8.2138888888888886</v>
+        <v>8.2166666666666668</v>
       </c>
       <c r="V53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>9.2138888888888886</v>
+        <v>9.2166666666666668</v>
       </c>
     </row>
     <row r="54" spans="2:24">
@@ -45008,7 +45095,7 @@
       <c r="Q54" s="4"/>
       <c r="V54" s="8">
         <f ca="1">SUM(M52:V52)</f>
-        <v>21699.048084267117</v>
+        <v>21697.05511892305</v>
       </c>
     </row>
     <row r="55" spans="2:24">
@@ -45050,7 +45137,7 @@
       <c r="U56" s="9"/>
       <c r="V56" s="50">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>29316.394128307908</v>
+        <v>29309.377136802548</v>
       </c>
     </row>
     <row r="57" spans="2:24">
@@ -45078,7 +45165,7 @@
       <c r="U57" s="34"/>
       <c r="V57" s="55">
         <f ca="1">V54+V56</f>
-        <v>51015.442212575028</v>
+        <v>51006.432255725595</v>
       </c>
     </row>
     <row r="58" spans="2:24">
@@ -45132,7 +45219,7 @@
       <c r="Q60" s="4"/>
       <c r="V60" s="46">
         <f ca="1">V57+V58-V59</f>
-        <v>42766.442212575028</v>
+        <v>42757.432255725595</v>
       </c>
     </row>
     <row r="61" spans="2:24">
@@ -45169,7 +45256,7 @@
       </c>
       <c r="V62" s="46">
         <f ca="1">V60/V61</f>
-        <v>348.81536470668891</v>
+        <v>348.74187691528448</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -45202,35 +45289,35 @@
     </row>
     <row r="68" spans="1:22">
       <c r="B68" s="35"/>
-      <c r="C68" s="150" t="s">
+      <c r="C68" s="151" t="s">
         <v>165</v>
       </c>
-      <c r="D68" s="150"/>
-      <c r="E68" s="150"/>
-      <c r="F68" s="150"/>
-      <c r="G68" s="150"/>
-      <c r="H68" s="150"/>
-      <c r="I68" s="150"/>
-      <c r="J68" s="151"/>
+      <c r="D68" s="151"/>
+      <c r="E68" s="151"/>
+      <c r="F68" s="151"/>
+      <c r="G68" s="151"/>
+      <c r="H68" s="151"/>
+      <c r="I68" s="151"/>
+      <c r="J68" s="152"/>
       <c r="M68" s="35"/>
-      <c r="N68" s="154" t="s">
+      <c r="N68" s="155" t="s">
         <v>537</v>
       </c>
-      <c r="O68" s="154"/>
-      <c r="P68" s="154"/>
-      <c r="Q68" s="154"/>
-      <c r="R68" s="154"/>
-      <c r="S68" s="154"/>
-      <c r="T68" s="154"/>
-      <c r="U68" s="155"/>
+      <c r="O68" s="155"/>
+      <c r="P68" s="155"/>
+      <c r="Q68" s="155"/>
+      <c r="R68" s="155"/>
+      <c r="S68" s="155"/>
+      <c r="T68" s="155"/>
+      <c r="U68" s="156"/>
     </row>
     <row r="69" spans="1:22" ht="15" customHeight="1">
-      <c r="B69" s="152" t="s">
+      <c r="B69" s="153" t="s">
         <v>164</v>
       </c>
       <c r="C69" s="36">
         <f ca="1">+J4</f>
-        <v>348.81536470668891</v>
+        <v>348.74187691528448</v>
       </c>
       <c r="D69" s="51">
         <v>5.0000000000000001E-3</v>
@@ -45253,12 +45340,12 @@
       <c r="J69" s="51">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="M69" s="152" t="s">
+      <c r="M69" s="153" t="s">
         <v>164</v>
       </c>
       <c r="N69" s="36">
         <f ca="1">+J4</f>
-        <v>348.81536470668891</v>
+        <v>348.74187691528448</v>
       </c>
       <c r="O69" s="51">
         <v>7.0000000000000007E-2</v>
@@ -45283,369 +45370,369 @@
       </c>
     </row>
     <row r="70" spans="1:22">
-      <c r="B70" s="152"/>
+      <c r="B70" s="153"/>
       <c r="C70" s="37">
         <v>0.06</v>
       </c>
       <c r="D70" s="38">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>600.29923167731761</v>
+        <v>600.21745199753741</v>
       </c>
       <c r="E70" s="38">
-        <v>622.07553439432354</v>
+        <v>621.99023032926971</v>
       </c>
       <c r="F70" s="38">
-        <v>648.39627040873825</v>
+        <v>648.30670646469559</v>
       </c>
       <c r="G70" s="52">
-        <v>680.96560220709034</v>
+        <v>680.87076708020038</v>
       </c>
       <c r="H70" s="38">
-        <v>722.46149941106648</v>
+        <v>722.35994838153147</v>
       </c>
       <c r="I70" s="38">
-        <v>777.34724472348012</v>
+        <v>777.23681071160297</v>
       </c>
       <c r="J70" s="38">
-        <v>853.65674700939235</v>
-      </c>
-      <c r="M70" s="152"/>
+        <v>853.53396268765846</v>
+      </c>
+      <c r="M70" s="153"/>
       <c r="N70" s="37">
         <v>0.06</v>
       </c>
       <c r="O70" s="38">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>622.98503351112299</v>
+        <v>622.89958224820316</v>
       </c>
       <c r="P70" s="38">
-        <v>647.14360380110941</v>
+        <v>647.05424259486858</v>
       </c>
       <c r="Q70" s="38">
-        <v>665.93360291554313</v>
+        <v>665.84120064227511</v>
       </c>
       <c r="R70" s="52">
-        <v>680.96560220709034</v>
+        <v>680.87076708020038</v>
       </c>
       <c r="S70" s="38">
-        <v>693.26451071835595</v>
+        <v>693.16768507486643</v>
       </c>
       <c r="T70" s="38">
-        <v>703.51360114441081</v>
+        <v>703.41511673708817</v>
       </c>
       <c r="U70" s="38">
-        <v>712.18590842799551</v>
+        <v>712.08602045127566</v>
       </c>
     </row>
     <row r="71" spans="1:22">
-      <c r="B71" s="152"/>
+      <c r="B71" s="153"/>
       <c r="C71" s="37">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="38">
-        <v>486.39771240361659</v>
+        <v>486.31987486589469</v>
       </c>
       <c r="E71" s="38">
-        <v>497.62625901364999</v>
+        <v>497.54631137342142</v>
       </c>
       <c r="F71" s="38">
-        <v>510.67519121046149</v>
+        <v>510.59279137535015</v>
       </c>
       <c r="G71" s="52">
-        <v>526.09062467008471</v>
+        <v>526.00532792000183</v>
       </c>
       <c r="H71" s="38">
-        <v>544.66139314678969</v>
+        <v>544.57260652161676</v>
       </c>
       <c r="I71" s="38">
-        <v>567.57074727198278</v>
+        <v>567.47765545155676</v>
       </c>
       <c r="J71" s="38">
-        <v>596.6780808950158</v>
-      </c>
-      <c r="M71" s="152"/>
+        <v>596.57951913624663</v>
+      </c>
+      <c r="M71" s="153"/>
       <c r="N71" s="37">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="38">
-        <v>483.55047379892966</v>
+        <v>483.47317132291465</v>
       </c>
       <c r="P71" s="38">
-        <v>501.27553666191085</v>
+        <v>501.19490323836766</v>
       </c>
       <c r="Q71" s="38">
-        <v>515.06169666645189</v>
+        <v>514.97847250594225</v>
       </c>
       <c r="R71" s="52">
-        <v>526.09062467008471</v>
+        <v>526.00532792000183</v>
       </c>
       <c r="S71" s="38">
-        <v>535.11429303669331</v>
+        <v>535.02730053150515</v>
       </c>
       <c r="T71" s="38">
-        <v>542.63401667553387</v>
+        <v>542.54561104109109</v>
       </c>
       <c r="U71" s="38">
-        <v>548.9968597545527</v>
+        <v>548.90725839535628</v>
       </c>
     </row>
     <row r="72" spans="1:22">
-      <c r="B72" s="152"/>
+      <c r="B72" s="153"/>
       <c r="C72" s="37">
         <v>0.08</v>
       </c>
       <c r="D72" s="52">
-        <v>403.29555318315931</v>
+        <v>403.22112242672432</v>
       </c>
       <c r="E72" s="52">
-        <v>409.00569286886383</v>
+        <v>408.93004152541562</v>
       </c>
       <c r="F72" s="52">
-        <v>415.42254515855763</v>
+        <v>415.34552216275034</v>
       </c>
       <c r="G72" s="52">
-        <v>422.72278820323783</v>
+        <v>422.64420472338924</v>
       </c>
       <c r="H72" s="52">
-        <v>431.14734675426445</v>
+        <v>431.06696245914247</v>
       </c>
       <c r="I72" s="52">
-        <v>441.03351546354168</v>
+        <v>440.95101792254451</v>
       </c>
       <c r="J72" s="52">
-        <v>452.86849771715265</v>
-      </c>
-      <c r="M72" s="152"/>
+        <v>452.78347035614502</v>
+      </c>
+      <c r="M72" s="153"/>
       <c r="N72" s="37">
         <v>0.08</v>
       </c>
       <c r="O72" s="52">
-        <v>390.18456206123454</v>
+        <v>390.11293388168457</v>
       </c>
       <c r="P72" s="52">
-        <v>403.74215628706924</v>
+        <v>403.66763006572813</v>
       </c>
       <c r="Q72" s="52">
-        <v>414.28695179605182</v>
+        <v>414.21017154220658</v>
       </c>
       <c r="R72" s="52">
-        <v>422.72278820323783</v>
+        <v>422.64420472338924</v>
       </c>
       <c r="S72" s="52">
-        <v>429.6248361727537</v>
+        <v>429.54477732617505</v>
       </c>
       <c r="T72" s="52">
-        <v>435.37654281401694</v>
+        <v>435.29525449516331</v>
       </c>
       <c r="U72" s="52">
-        <v>440.24337151047041</v>
+        <v>440.16104286892244</v>
       </c>
     </row>
     <row r="73" spans="1:22">
-      <c r="B73" s="152"/>
+      <c r="B73" s="153"/>
       <c r="C73" s="37">
         <v>0.09</v>
       </c>
       <c r="D73" s="38">
-        <v>340.10201557885489</v>
+        <v>340.03061336102229</v>
       </c>
       <c r="E73" s="38">
-        <v>342.7716099333025</v>
+        <v>342.69956873781035</v>
       </c>
       <c r="F73" s="38">
-        <v>345.66040261892516</v>
+        <v>345.5876699798111</v>
       </c>
       <c r="G73" s="52">
-        <v>348.81536470668891</v>
+        <v>348.74187691528448</v>
       </c>
       <c r="H73" s="38">
-        <v>352.29791990478003</v>
+        <v>352.22359855041645</v>
       </c>
       <c r="I73" s="38">
-        <v>356.18996649078048</v>
+        <v>356.11471356012163</v>
       </c>
       <c r="J73" s="38">
-        <v>360.60318393412007</v>
-      </c>
-      <c r="M73" s="152"/>
+        <v>360.52687468292009</v>
+      </c>
+      <c r="M73" s="153"/>
       <c r="N73" s="37">
         <v>0.09</v>
       </c>
       <c r="O73" s="38">
-        <v>323.19612369326933</v>
+        <v>323.12876796557583</v>
       </c>
       <c r="P73" s="38">
-        <v>333.87080744886083</v>
+        <v>333.80089669462109</v>
       </c>
       <c r="Q73" s="38">
-        <v>342.17333925876534</v>
+        <v>342.1014412616563</v>
       </c>
       <c r="R73" s="52">
-        <v>348.81536470668891</v>
+        <v>348.74187691528448</v>
       </c>
       <c r="S73" s="38">
-        <v>354.24974916408092</v>
+        <v>354.17496063188946</v>
       </c>
       <c r="T73" s="38">
-        <v>358.7784028785743</v>
+        <v>358.70253039572685</v>
       </c>
       <c r="U73" s="38">
-        <v>362.61034063699168</v>
+        <v>362.53355096512769</v>
       </c>
     </row>
     <row r="74" spans="1:22">
-      <c r="B74" s="152"/>
+      <c r="B74" s="153"/>
       <c r="C74" s="37">
         <v>0.1</v>
       </c>
       <c r="D74" s="38">
-        <v>290.5130759585993</v>
+        <v>290.44441719648836</v>
       </c>
       <c r="E74" s="38">
-        <v>291.45591360100627</v>
+        <v>291.38700525519869</v>
       </c>
       <c r="F74" s="38">
-        <v>292.3987512434133</v>
+        <v>292.32959331390919</v>
       </c>
       <c r="G74" s="52">
-        <v>293.34158888582039</v>
+        <v>293.27218137261963</v>
       </c>
       <c r="H74" s="38">
-        <v>294.28442652822724</v>
+        <v>294.21476943132996</v>
       </c>
       <c r="I74" s="38">
-        <v>295.22726417063427</v>
+        <v>295.1573574900404</v>
       </c>
       <c r="J74" s="38">
-        <v>296.1701018130413</v>
-      </c>
-      <c r="M74" s="152"/>
+        <v>296.09994554875084</v>
+      </c>
+      <c r="M74" s="153"/>
       <c r="N74" s="37">
         <v>0.1</v>
       </c>
       <c r="O74" s="38">
-        <v>272.73385184463882</v>
+        <v>272.66989951794892</v>
       </c>
       <c r="P74" s="38">
-        <v>281.32040894513108</v>
+        <v>281.25418362406174</v>
       </c>
       <c r="Q74" s="38">
-        <v>287.99884224551403</v>
+        <v>287.93084903992718</v>
       </c>
       <c r="R74" s="52">
-        <v>293.34158888582039</v>
+        <v>293.27218137261963</v>
       </c>
       <c r="S74" s="38">
-        <v>297.71292704607089</v>
+        <v>297.64236237209519</v>
       </c>
       <c r="T74" s="38">
-        <v>301.35570884627981</v>
+        <v>301.28417987165824</v>
       </c>
       <c r="U74" s="38">
-        <v>304.43806267722573</v>
+        <v>304.3657177559038</v>
       </c>
     </row>
     <row r="75" spans="1:22">
-      <c r="B75" s="152"/>
+      <c r="B75" s="153"/>
       <c r="C75" s="37">
         <v>0.11</v>
       </c>
       <c r="D75" s="38">
-        <v>250.62720498760166</v>
+        <v>250.56106409055718</v>
       </c>
       <c r="E75" s="38">
-        <v>250.57763879321493</v>
+        <v>250.51151226277906</v>
       </c>
       <c r="F75" s="38">
-        <v>250.4315489571276</v>
+        <v>250.36546477038041</v>
       </c>
       <c r="G75" s="52">
-        <v>250.17284820572306</v>
+        <v>250.10683900259124</v>
       </c>
       <c r="H75" s="38">
-        <v>249.78166402453334</v>
+        <v>249.71576820493078</v>
       </c>
       <c r="I75" s="38">
-        <v>249.23315577047399</v>
+        <v>249.16741893429824</v>
       </c>
       <c r="J75" s="38">
-        <v>248.49585862897089</v>
-      </c>
-      <c r="M75" s="152"/>
+        <v>248.43033549609899</v>
+      </c>
+      <c r="M75" s="153"/>
       <c r="N75" s="37">
         <v>0.11</v>
       </c>
       <c r="O75" s="38">
-        <v>233.32034211422379</v>
+        <v>233.25921755803853</v>
       </c>
       <c r="P75" s="38">
-        <v>240.34221965234846</v>
+        <v>240.27905982660224</v>
       </c>
       <c r="Q75" s="38">
-        <v>245.8036799597788</v>
+        <v>245.7389371465961</v>
       </c>
       <c r="R75" s="52">
-        <v>250.17284820572306</v>
+        <v>250.10683900259124</v>
       </c>
       <c r="S75" s="38">
-        <v>253.74762222513192</v>
+        <v>253.68057688476912</v>
       </c>
       <c r="T75" s="38">
-        <v>256.72660057463941</v>
+        <v>256.65869178658403</v>
       </c>
       <c r="U75" s="38">
-        <v>259.2472745626842</v>
+        <v>259.17863516504269</v>
       </c>
     </row>
     <row r="76" spans="1:22">
-      <c r="B76" s="153"/>
+      <c r="B76" s="154"/>
       <c r="C76" s="37">
         <v>0.12</v>
       </c>
       <c r="D76" s="38">
-        <v>217.90074500540914</v>
+        <v>217.83693670761056</v>
       </c>
       <c r="E76" s="38">
-        <v>217.28521502181749</v>
+        <v>217.22160046353318</v>
       </c>
       <c r="F76" s="38">
-        <v>216.53500497344007</v>
+        <v>216.47162654553802</v>
       </c>
       <c r="G76" s="52">
-        <v>215.62991285055892</v>
+        <v>215.5668193025374</v>
       </c>
       <c r="H76" s="38">
-        <v>214.54548358877869</v>
+        <v>214.48273136742512</v>
       </c>
       <c r="I76" s="38">
-        <v>213.25182766494962</v>
+        <v>213.1894826248494</v>
       </c>
       <c r="J76" s="38">
-        <v>211.71202272694529</v>
-      </c>
-      <c r="M76" s="153"/>
+        <v>211.65016234408128</v>
+      </c>
+      <c r="M76" s="154"/>
       <c r="N76" s="37">
         <v>0.12</v>
       </c>
       <c r="O76" s="38">
-        <v>201.66563438324948</v>
+        <v>201.60693612481319</v>
       </c>
       <c r="P76" s="38">
-        <v>207.48408374462844</v>
+        <v>207.42355411553163</v>
       </c>
       <c r="Q76" s="38">
-        <v>212.00954435903427</v>
+        <v>211.94759033053484</v>
       </c>
       <c r="R76" s="52">
-        <v>215.62991285055892</v>
+        <v>215.5668193025374</v>
       </c>
       <c r="S76" s="38">
-        <v>218.59203252544273</v>
+        <v>218.52800664326671</v>
       </c>
       <c r="T76" s="38">
-        <v>221.06046558784595</v>
+        <v>220.99566276054122</v>
       </c>
       <c r="U76" s="38">
-        <v>223.14913971757173</v>
+        <v>223.08367947515811</v>
       </c>
     </row>
   </sheetData>
@@ -47974,23 +48061,23 @@
     <row r="3" spans="1:35">
       <c r="A3" s="92"/>
       <c r="B3" s="91"/>
-      <c r="C3" s="156" t="s">
+      <c r="C3" s="157" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="156"/>
-      <c r="E3" s="156"/>
-      <c r="F3" s="156"/>
-      <c r="G3" s="156"/>
-      <c r="H3" s="156"/>
-      <c r="I3" s="156"/>
-      <c r="J3" s="156" t="s">
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="157" t="s">
         <v>118</v>
       </c>
-      <c r="K3" s="156"/>
-      <c r="L3" s="156"/>
-      <c r="M3" s="156"/>
-      <c r="N3" s="156"/>
-      <c r="O3" s="156"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="157"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="157"/>
+      <c r="O3" s="157"/>
       <c r="P3" s="91"/>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>

--- a/KER.PA.xlsx
+++ b/KER.PA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BE5EE3-8D4A-4F83-84DE-AD489149F947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6491B2-FE07-482D-99D2-3E98C136B354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="1" xr2:uid="{00BE0985-5336-41E3-B925-F565FA10FCAA}"/>
+    <workbookView xWindow="225" yWindow="3120" windowWidth="38175" windowHeight="15240" xr2:uid="{00BE0985-5336-41E3-B925-F565FA10FCAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -121,6 +121,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={03B45DC8-9325-42B7-8AA9-B57F9493EAB8}</author>
+    <author>tc={AB67C310-CB2C-4A4B-BCC4-F1B9C1CD3E61}</author>
   </authors>
   <commentList>
     <comment ref="P10" authorId="0" shapeId="0" xr:uid="{03B45DC8-9325-42B7-8AA9-B57F9493EAB8}">
@@ -129,6 +130,14 @@
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Analysist Consensus 3730</t>
+      </text>
+    </comment>
+    <comment ref="S18" authorId="1" shapeId="0" xr:uid="{AB67C310-CB2C-4A4B-BCC4-F1B9C1CD3E61}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    At constant fx 0%</t>
       </text>
     </comment>
   </commentList>
@@ -192,7 +201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="553">
   <si>
     <t>Kering</t>
   </si>
@@ -1837,6 +1846,21 @@
   </si>
   <si>
     <t>created surge in Website traffic: jumped to 316.000 (average 180-210.000) visitors per day</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Partnership between Kering Eyewear and Google to launch Smart Glasses under Gucci Brand</t>
   </si>
 </sst>
 </file>
@@ -1854,13 +1878,25 @@
     <numFmt numFmtId="171" formatCode="#,##0.00;\(#,##0.00\)"/>
     <numFmt numFmtId="172" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2336,27 +2372,27 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2367,41 +2403,41 @@
     <xf numFmtId="9" fontId="0" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="0" fillId="8" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="8" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="19" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="165" fontId="8" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2417,8 +2453,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="13" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2429,188 +2465,192 @@
     <xf numFmtId="167" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="26" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="26" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="33" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="35" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="24" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="33" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -7344,16 +7384,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>604835</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>9523</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>47626</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>4760</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>19048</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:rowOff>138113</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7368,7 +7408,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="11320460" y="0"/>
+          <a:off x="11944348" y="47626"/>
           <a:ext cx="9525" cy="3167062"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -7848,12 +7888,15 @@
   <threadedComment ref="P10" dT="2025-07-28T12:08:56.11" personId="{ABA52468-0383-464D-BC04-700532FCBC75}" id="{03B45DC8-9325-42B7-8AA9-B57F9493EAB8}">
     <text>Analysist Consensus 3730</text>
   </threadedComment>
+  <threadedComment ref="S18" dT="2026-04-17T15:39:38.68" personId="{ABA52468-0383-464D-BC04-700532FCBC75}" id="{AB67C310-CB2C-4A4B-BCC4-F1B9C1CD3E61}">
+    <text>At constant fx 0%</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30076D03-558C-464F-8F0F-AA9F5CEE4D93}">
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="58" customWidth="1"/>
@@ -7879,7 +7922,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="58">
-        <v>284.8</v>
+        <v>256.14999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7889,8 +7932,8 @@
       <c r="H3" s="62">
         <v>122.604812</v>
       </c>
-      <c r="I3" s="148" t="s">
-        <v>513</v>
+      <c r="I3" s="151" t="s">
+        <v>548</v>
       </c>
       <c r="M3" s="61"/>
     </row>
@@ -7903,7 +7946,7 @@
       </c>
       <c r="H4" s="62">
         <f>H3*H2</f>
-        <v>34917.850457599998</v>
+        <v>31405.222593799997</v>
       </c>
       <c r="K4" s="61"/>
       <c r="N4" s="62"/>
@@ -7918,8 +7961,8 @@
       <c r="H5" s="62">
         <v>4313</v>
       </c>
-      <c r="I5" s="148" t="s">
-        <v>513</v>
+      <c r="I5" s="151" t="s">
+        <v>548</v>
       </c>
       <c r="N5" s="62"/>
     </row>
@@ -7931,8 +7974,8 @@
         <f>10306+2046+170+40</f>
         <v>12562</v>
       </c>
-      <c r="I6" s="148" t="s">
-        <v>513</v>
+      <c r="I6" s="151" t="s">
+        <v>548</v>
       </c>
       <c r="N6" s="62"/>
     </row>
@@ -7954,7 +7997,7 @@
       </c>
       <c r="H7" s="62">
         <f>H4+H6-H5</f>
-        <v>43166.850457599998</v>
+        <v>39654.222593799997</v>
       </c>
       <c r="N7" s="62"/>
     </row>
@@ -8276,13 +8319,18 @@
       </c>
     </row>
     <row r="58" spans="2:2">
-      <c r="B58" s="149" t="s">
+      <c r="B58" s="148" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="59" spans="2:2">
-      <c r="B59" s="150" t="s">
+      <c r="B59" s="149" t="s">
         <v>544</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="153" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -8327,7 +8375,7 @@
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="63"/>
-      <c r="T4" s="158" t="s">
+      <c r="T4" s="150" t="s">
         <v>545</v>
       </c>
     </row>
@@ -8430,7 +8478,7 @@
       <c r="D24" s="58" t="s">
         <v>400</v>
       </c>
-      <c r="T24" s="158" t="s">
+      <c r="T24" s="150" t="s">
         <v>547</v>
       </c>
     </row>
@@ -28952,6 +29000,18 @@
       <c r="R2" s="140" t="s">
         <v>513</v>
       </c>
+      <c r="S2" s="140" t="s">
+        <v>548</v>
+      </c>
+      <c r="T2" s="140" t="s">
+        <v>549</v>
+      </c>
+      <c r="U2" s="140" t="s">
+        <v>550</v>
+      </c>
+      <c r="V2" s="140" t="s">
+        <v>551</v>
+      </c>
     </row>
     <row r="3" spans="1:38">
       <c r="A3" s="141" t="s">
@@ -29029,7 +29089,9 @@
         <f>+Model!AB38-SUM(O4:Q4)</f>
         <v>1622</v>
       </c>
-      <c r="S4" s="143"/>
+      <c r="S4" s="143">
+        <v>1347</v>
+      </c>
       <c r="T4" s="143"/>
       <c r="U4" s="143"/>
       <c r="V4" s="143"/>
@@ -29106,7 +29168,9 @@
         <f>+Model!AB39-SUM(O5:Q5)</f>
         <v>735</v>
       </c>
-      <c r="S5" s="143"/>
+      <c r="S5" s="152" t="s">
+        <v>136</v>
+      </c>
       <c r="T5" s="143"/>
       <c r="U5" s="143"/>
       <c r="V5" s="143"/>
@@ -29183,7 +29247,9 @@
         <f>+Model!AB40-SUM(O6:Q6)</f>
         <v>467</v>
       </c>
-      <c r="S6" s="143"/>
+      <c r="S6" s="152" t="s">
+        <v>136</v>
+      </c>
       <c r="T6" s="143"/>
       <c r="U6" s="143"/>
       <c r="V6" s="143"/>
@@ -29260,7 +29326,9 @@
         <f>+Model!AB41-SUM(O7:Q7)</f>
         <v>789</v>
       </c>
-      <c r="S7" s="143"/>
+      <c r="S7" s="152" t="s">
+        <v>136</v>
+      </c>
       <c r="T7" s="143"/>
       <c r="U7" s="143"/>
       <c r="V7" s="143"/>
@@ -29337,7 +29405,9 @@
         <f>+Model!AB42-SUM(O8:Q8)</f>
         <v>91</v>
       </c>
-      <c r="S8" s="143"/>
+      <c r="S8" s="143">
+        <v>489</v>
+      </c>
       <c r="T8" s="143"/>
       <c r="U8" s="143"/>
       <c r="V8" s="143"/>
@@ -29414,7 +29484,9 @@
         <f>+Model!AB43-SUM(O9:Q9)</f>
         <v>-31</v>
       </c>
-      <c r="S9" s="143"/>
+      <c r="S9" s="143">
+        <v>-72</v>
+      </c>
       <c r="T9" s="143"/>
       <c r="U9" s="143"/>
       <c r="V9" s="143"/>
@@ -29501,7 +29573,9 @@
         <f>+SUM(R4:R9)</f>
         <v>3673</v>
       </c>
-      <c r="S10" s="143"/>
+      <c r="S10" s="143">
+        <v>3568</v>
+      </c>
       <c r="T10" s="143"/>
       <c r="U10" s="143"/>
       <c r="V10" s="143"/>
@@ -29621,7 +29695,7 @@
       </c>
       <c r="S12" s="146">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.14258434118395924</v>
       </c>
       <c r="T12" s="143"/>
       <c r="U12" s="143"/>
@@ -29699,9 +29773,8 @@
         <f t="shared" si="8"/>
         <v>-4.5454545454545414E-2</v>
       </c>
-      <c r="S13" s="146">
-        <f t="shared" si="8"/>
-        <v>-1</v>
+      <c r="S13" s="152" t="s">
+        <v>136</v>
       </c>
       <c r="T13" s="143"/>
       <c r="U13" s="143"/>
@@ -29779,9 +29852,8 @@
         <f t="shared" si="8"/>
         <v>-2.7083333333333348E-2</v>
       </c>
-      <c r="S14" s="146">
-        <f t="shared" si="8"/>
-        <v>-1</v>
+      <c r="S14" s="152" t="s">
+        <v>136</v>
       </c>
       <c r="T14" s="143"/>
       <c r="U14" s="143"/>
@@ -29859,9 +29931,8 @@
         <f t="shared" si="8"/>
         <v>-3.5452322738386277E-2</v>
       </c>
-      <c r="S15" s="146">
-        <f t="shared" si="8"/>
-        <v>-1</v>
+      <c r="S15" s="152" t="s">
+        <v>136</v>
       </c>
       <c r="T15" s="143"/>
       <c r="U15" s="143"/>
@@ -29941,7 +30012,7 @@
       </c>
       <c r="S16" s="146">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>-0.12365591397849462</v>
       </c>
       <c r="T16" s="143"/>
       <c r="U16" s="143"/>
@@ -30021,7 +30092,7 @@
       </c>
       <c r="S17" s="146">
         <f t="shared" si="8"/>
-        <v>-1</v>
+        <v>0.14285714285714279</v>
       </c>
       <c r="T17" s="143"/>
       <c r="U17" s="143"/>
@@ -30101,7 +30172,7 @@
       </c>
       <c r="S18" s="147">
         <f t="shared" si="12"/>
-        <v>-1</v>
+        <v>-8.1122843162503178E-2</v>
       </c>
       <c r="T18" s="143"/>
       <c r="U18" s="143"/>
@@ -43337,14 +43408,14 @@
       </c>
       <c r="J3" s="14">
         <f>+Main!H2</f>
-        <v>284.8</v>
+        <v>256.14999999999998</v>
       </c>
       <c r="L3" t="s">
         <v>151</v>
       </c>
       <c r="O3" s="14">
         <f>+J3</f>
-        <v>284.8</v>
+        <v>256.14999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -43353,14 +43424,14 @@
       </c>
       <c r="E4" s="48">
         <f ca="1">+TODAY()</f>
-        <v>46099</v>
+        <v>46143</v>
       </c>
       <c r="G4" t="s">
         <v>152</v>
       </c>
       <c r="J4" s="56">
         <f ca="1">V62</f>
-        <v>348.74187691528448</v>
+        <v>345.59261421468523</v>
       </c>
       <c r="L4" t="s">
         <v>534</v>
@@ -43382,7 +43453,7 @@
       </c>
       <c r="J5" s="16">
         <f ca="1">J4/J3-1</f>
-        <v>0.22451501725872358</v>
+        <v>0.34918061376023912</v>
       </c>
       <c r="L5" t="s">
         <v>154</v>
@@ -45001,43 +45072,43 @@
       <c r="L52" s="44"/>
       <c r="M52" s="44">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>249.66124061830087</v>
+        <v>383.32884859296615</v>
       </c>
       <c r="N52" s="44">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>1390.3271785388665</v>
+        <v>1376.0893233613535</v>
       </c>
       <c r="O52" s="44">
         <f t="shared" ref="O52:U52" ca="1" si="23">O51/(1+$E$18)^O53</f>
-        <v>1761.253506316421</v>
+        <v>1743.2171241317808</v>
       </c>
       <c r="P52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2110.1757089231983</v>
+        <v>2088.5661362941655</v>
       </c>
       <c r="Q52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2651.7534009292303</v>
+        <v>2624.5977202580189</v>
       </c>
       <c r="R52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2768.9248225423171</v>
+        <v>2740.5692302548896</v>
       </c>
       <c r="S52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2870.067206499938</v>
+        <v>2840.6758503740953</v>
       </c>
       <c r="T52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2826.5522329243936</v>
+        <v>2797.6064984488967</v>
       </c>
       <c r="U52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2627.9901480785911</v>
+        <v>2601.0778185824533</v>
       </c>
       <c r="V52" s="45">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>2440.3496735517915</v>
+        <v>2415.3589046372144</v>
       </c>
     </row>
     <row r="53" spans="2:24">
@@ -45046,43 +45117,43 @@
       </c>
       <c r="M53" s="53">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.21666666666666667</v>
+        <v>0.33611111111111114</v>
       </c>
       <c r="N53" s="53">
         <f ca="1">M53+1</f>
-        <v>1.2166666666666668</v>
+        <v>1.3361111111111112</v>
       </c>
       <c r="O53" s="53">
         <f ca="1">N53+1</f>
-        <v>2.2166666666666668</v>
+        <v>2.3361111111111112</v>
       </c>
       <c r="P53" s="53">
         <f t="shared" ref="P53:V53" ca="1" si="24">O53+1</f>
-        <v>3.2166666666666668</v>
+        <v>3.3361111111111112</v>
       </c>
       <c r="Q53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>4.2166666666666668</v>
+        <v>4.3361111111111112</v>
       </c>
       <c r="R53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>5.2166666666666668</v>
+        <v>5.3361111111111112</v>
       </c>
       <c r="S53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>6.2166666666666668</v>
+        <v>6.3361111111111112</v>
       </c>
       <c r="T53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>7.2166666666666668</v>
+        <v>7.3361111111111112</v>
       </c>
       <c r="U53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>8.2166666666666668</v>
+        <v>8.3361111111111121</v>
       </c>
       <c r="V53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>9.2166666666666668</v>
+        <v>9.3361111111111121</v>
       </c>
     </row>
     <row r="54" spans="2:24">
@@ -45095,7 +45166,7 @@
       <c r="Q54" s="4"/>
       <c r="V54" s="8">
         <f ca="1">SUM(M52:V52)</f>
-        <v>21697.05511892305</v>
+        <v>21611.087454935834</v>
       </c>
     </row>
     <row r="55" spans="2:24">
@@ -45137,7 +45208,7 @@
       <c r="U56" s="9"/>
       <c r="V56" s="50">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>29309.377136802548</v>
+        <v>29009.230039444174</v>
       </c>
     </row>
     <row r="57" spans="2:24">
@@ -45165,7 +45236,7 @@
       <c r="U57" s="34"/>
       <c r="V57" s="55">
         <f ca="1">V54+V56</f>
-        <v>51006.432255725595</v>
+        <v>50620.317494380011</v>
       </c>
     </row>
     <row r="58" spans="2:24">
@@ -45219,7 +45290,7 @@
       <c r="Q60" s="4"/>
       <c r="V60" s="46">
         <f ca="1">V57+V58-V59</f>
-        <v>42757.432255725595</v>
+        <v>42371.317494380011</v>
       </c>
     </row>
     <row r="61" spans="2:24">
@@ -45256,7 +45327,7 @@
       </c>
       <c r="V62" s="46">
         <f ca="1">V60/V61</f>
-        <v>348.74187691528448</v>
+        <v>345.59261421468523</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -45289,35 +45360,35 @@
     </row>
     <row r="68" spans="1:22">
       <c r="B68" s="35"/>
-      <c r="C68" s="151" t="s">
+      <c r="C68" s="154" t="s">
         <v>165</v>
       </c>
-      <c r="D68" s="151"/>
-      <c r="E68" s="151"/>
-      <c r="F68" s="151"/>
-      <c r="G68" s="151"/>
-      <c r="H68" s="151"/>
-      <c r="I68" s="151"/>
-      <c r="J68" s="152"/>
+      <c r="D68" s="154"/>
+      <c r="E68" s="154"/>
+      <c r="F68" s="154"/>
+      <c r="G68" s="154"/>
+      <c r="H68" s="154"/>
+      <c r="I68" s="154"/>
+      <c r="J68" s="155"/>
       <c r="M68" s="35"/>
-      <c r="N68" s="155" t="s">
+      <c r="N68" s="158" t="s">
         <v>537</v>
       </c>
-      <c r="O68" s="155"/>
-      <c r="P68" s="155"/>
-      <c r="Q68" s="155"/>
-      <c r="R68" s="155"/>
-      <c r="S68" s="155"/>
-      <c r="T68" s="155"/>
-      <c r="U68" s="156"/>
+      <c r="O68" s="158"/>
+      <c r="P68" s="158"/>
+      <c r="Q68" s="158"/>
+      <c r="R68" s="158"/>
+      <c r="S68" s="158"/>
+      <c r="T68" s="158"/>
+      <c r="U68" s="159"/>
     </row>
     <row r="69" spans="1:22" ht="15" customHeight="1">
-      <c r="B69" s="153" t="s">
+      <c r="B69" s="156" t="s">
         <v>164</v>
       </c>
       <c r="C69" s="36">
         <f ca="1">+J4</f>
-        <v>348.74187691528448</v>
+        <v>345.59261421468523</v>
       </c>
       <c r="D69" s="51">
         <v>5.0000000000000001E-3</v>
@@ -45340,12 +45411,12 @@
       <c r="J69" s="51">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="M69" s="153" t="s">
+      <c r="M69" s="156" t="s">
         <v>164</v>
       </c>
       <c r="N69" s="36">
         <f ca="1">+J4</f>
-        <v>348.74187691528448</v>
+        <v>345.59261421468523</v>
       </c>
       <c r="O69" s="51">
         <v>7.0000000000000007E-2</v>
@@ -45370,369 +45441,369 @@
       </c>
     </row>
     <row r="70" spans="1:22">
-      <c r="B70" s="153"/>
+      <c r="B70" s="156"/>
       <c r="C70" s="37">
         <v>0.06</v>
       </c>
       <c r="D70" s="38">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>600.21745199753741</v>
+        <v>596.70941523707836</v>
       </c>
       <c r="E70" s="38">
-        <v>621.99023032926971</v>
+        <v>618.33118338367001</v>
       </c>
       <c r="F70" s="38">
-        <v>648.30670646469559</v>
+        <v>644.46513545749406</v>
       </c>
       <c r="G70" s="52">
-        <v>680.87076708020038</v>
+        <v>676.803340431263</v>
       </c>
       <c r="H70" s="38">
-        <v>722.35994838153147</v>
+        <v>718.00476383352429</v>
       </c>
       <c r="I70" s="38">
-        <v>777.23681071160297</v>
+        <v>772.50101487852476</v>
       </c>
       <c r="J70" s="38">
-        <v>853.53396268765846</v>
-      </c>
-      <c r="M70" s="153"/>
+        <v>848.26899015190713</v>
+      </c>
+      <c r="M70" s="156"/>
       <c r="N70" s="37">
         <v>0.06</v>
       </c>
       <c r="O70" s="38">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>622.89958224820316</v>
+        <v>619.23422828015805</v>
       </c>
       <c r="P70" s="38">
-        <v>647.05424259486858</v>
+        <v>643.22135834311837</v>
       </c>
       <c r="Q70" s="38">
-        <v>665.84120064227511</v>
+        <v>661.87801505875439</v>
       </c>
       <c r="R70" s="52">
-        <v>680.87076708020038</v>
+        <v>676.803340431263</v>
       </c>
       <c r="S70" s="38">
-        <v>693.16768507486643</v>
+        <v>689.01497028149743</v>
       </c>
       <c r="T70" s="38">
-        <v>703.41511673708817</v>
+        <v>699.19132849002608</v>
       </c>
       <c r="U70" s="38">
-        <v>712.08602045127566</v>
+        <v>707.80209312801196</v>
       </c>
     </row>
     <row r="71" spans="1:22">
-      <c r="B71" s="153"/>
+      <c r="B71" s="156"/>
       <c r="C71" s="37">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="38">
-        <v>486.31987486589469</v>
+        <v>482.98202668795193</v>
       </c>
       <c r="E71" s="38">
-        <v>497.54631137342142</v>
+        <v>494.1181029265378</v>
       </c>
       <c r="F71" s="38">
-        <v>510.59279137535015</v>
+        <v>507.05957334319748</v>
       </c>
       <c r="G71" s="52">
-        <v>526.00532792000183</v>
+        <v>522.34805619135307</v>
       </c>
       <c r="H71" s="38">
-        <v>544.57260652161676</v>
+        <v>540.76588894816973</v>
       </c>
       <c r="I71" s="38">
-        <v>567.47765545155676</v>
+        <v>563.48657782939563</v>
       </c>
       <c r="J71" s="38">
-        <v>596.57951913624663</v>
-      </c>
-      <c r="M71" s="153"/>
+        <v>592.35420403120611</v>
+      </c>
+      <c r="M71" s="156"/>
       <c r="N71" s="37">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="38">
-        <v>483.47317132291465</v>
+        <v>480.1582359274534</v>
       </c>
       <c r="P71" s="38">
-        <v>501.19490323836766</v>
+        <v>497.73732770407815</v>
       </c>
       <c r="Q71" s="38">
-        <v>514.97847250594225</v>
+        <v>511.40995464145311</v>
       </c>
       <c r="R71" s="52">
-        <v>526.00532792000183</v>
+        <v>522.34805619135307</v>
       </c>
       <c r="S71" s="38">
-        <v>535.02730053150515</v>
+        <v>531.29741200490753</v>
       </c>
       <c r="T71" s="38">
-        <v>542.54561104109109</v>
+        <v>538.75520851620297</v>
       </c>
       <c r="U71" s="38">
-        <v>548.90725839535628</v>
+        <v>545.06565171806812</v>
       </c>
     </row>
     <row r="72" spans="1:22">
-      <c r="B72" s="153"/>
+      <c r="B72" s="156"/>
       <c r="C72" s="37">
         <v>0.08</v>
       </c>
       <c r="D72" s="52">
-        <v>403.22112242672432</v>
+        <v>400.03034784046696</v>
       </c>
       <c r="E72" s="52">
-        <v>408.93004152541562</v>
+        <v>405.68702778144677</v>
       </c>
       <c r="F72" s="52">
-        <v>415.34552216275034</v>
+        <v>412.04380390764453</v>
       </c>
       <c r="G72" s="52">
-        <v>422.64420472338924</v>
+        <v>419.27570026536478</v>
       </c>
       <c r="H72" s="52">
-        <v>431.06696245914247</v>
+        <v>427.62138600865893</v>
       </c>
       <c r="I72" s="52">
-        <v>440.95101792254451</v>
+        <v>437.41499795319947</v>
       </c>
       <c r="J72" s="52">
-        <v>452.78347035614502</v>
-      </c>
-      <c r="M72" s="153"/>
+        <v>449.13917816606823</v>
+      </c>
+      <c r="M72" s="156"/>
       <c r="N72" s="37">
         <v>0.08</v>
       </c>
       <c r="O72" s="52">
-        <v>390.11293388168457</v>
+        <v>387.04210507095462</v>
       </c>
       <c r="P72" s="52">
-        <v>403.66763006572813</v>
+        <v>400.47276973529227</v>
       </c>
       <c r="Q72" s="52">
-        <v>414.21017154220658</v>
+        <v>410.91884225199925</v>
       </c>
       <c r="R72" s="52">
-        <v>422.64420472338924</v>
+        <v>419.27570026536478</v>
       </c>
       <c r="S72" s="52">
-        <v>429.54477732617505</v>
+        <v>426.11312954902752</v>
       </c>
       <c r="T72" s="52">
-        <v>435.29525449516331</v>
+        <v>431.81098728541326</v>
       </c>
       <c r="U72" s="52">
-        <v>440.16104286892244</v>
+        <v>436.63225152389339</v>
       </c>
     </row>
     <row r="73" spans="1:22">
-      <c r="B73" s="153"/>
+      <c r="B73" s="156"/>
       <c r="C73" s="37">
         <v>0.09</v>
       </c>
       <c r="D73" s="38">
-        <v>340.03061336102229</v>
+        <v>336.97055966878679</v>
       </c>
       <c r="E73" s="38">
-        <v>342.69956873781035</v>
+        <v>339.61218320547522</v>
       </c>
       <c r="F73" s="38">
-        <v>345.5876699798111</v>
+        <v>342.4707084110895</v>
       </c>
       <c r="G73" s="52">
-        <v>348.74187691528448</v>
+        <v>345.59261421468523</v>
       </c>
       <c r="H73" s="38">
-        <v>352.22359855041645</v>
+        <v>349.03868075425788</v>
       </c>
       <c r="I73" s="38">
-        <v>356.11471356012163</v>
+        <v>352.88994821380197</v>
       </c>
       <c r="J73" s="38">
-        <v>360.52687468292009</v>
-      </c>
-      <c r="M73" s="153"/>
+        <v>357.2569259351277</v>
+      </c>
+      <c r="M73" s="156"/>
       <c r="N73" s="37">
         <v>0.09</v>
       </c>
       <c r="O73" s="38">
-        <v>323.12876796557583</v>
+        <v>320.24180017044978</v>
       </c>
       <c r="P73" s="38">
-        <v>333.80089669462109</v>
+        <v>330.80463935554792</v>
       </c>
       <c r="Q73" s="38">
-        <v>342.1014412616563</v>
+        <v>339.02018094395754</v>
       </c>
       <c r="R73" s="52">
-        <v>348.74187691528448</v>
+        <v>345.59261421468523</v>
       </c>
       <c r="S73" s="38">
-        <v>354.17496063188946</v>
+        <v>350.97005961800784</v>
       </c>
       <c r="T73" s="38">
-        <v>358.70253039572685</v>
+        <v>355.45126412077678</v>
       </c>
       <c r="U73" s="38">
-        <v>362.53355096512769</v>
+        <v>359.24305254619657</v>
       </c>
     </row>
     <row r="74" spans="1:22">
-      <c r="B74" s="153"/>
+      <c r="B74" s="156"/>
       <c r="C74" s="37">
         <v>0.1</v>
       </c>
       <c r="D74" s="38">
-        <v>290.44441719648836</v>
+        <v>287.50274393382966</v>
       </c>
       <c r="E74" s="38">
-        <v>291.38700525519869</v>
+        <v>288.43466216353943</v>
       </c>
       <c r="F74" s="38">
-        <v>292.32959331390919</v>
+        <v>289.36658039324919</v>
       </c>
       <c r="G74" s="52">
-        <v>293.27218137261963</v>
+        <v>290.29849862295896</v>
       </c>
       <c r="H74" s="38">
-        <v>294.21476943132996</v>
+        <v>291.23041685266867</v>
       </c>
       <c r="I74" s="38">
-        <v>295.1573574900404</v>
+        <v>292.16233508237849</v>
       </c>
       <c r="J74" s="38">
-        <v>296.09994554875084</v>
-      </c>
-      <c r="M74" s="153"/>
+        <v>293.0942533120882</v>
+      </c>
+      <c r="M74" s="156"/>
       <c r="N74" s="37">
         <v>0.1</v>
       </c>
       <c r="O74" s="38">
-        <v>272.66989951794892</v>
+        <v>269.92942874501676</v>
       </c>
       <c r="P74" s="38">
-        <v>281.25418362406174</v>
+        <v>278.41654119415938</v>
       </c>
       <c r="Q74" s="38">
-        <v>287.93084903992718</v>
+        <v>285.01762865460358</v>
       </c>
       <c r="R74" s="52">
-        <v>293.27218137261963</v>
+        <v>290.29849862295896</v>
       </c>
       <c r="S74" s="38">
-        <v>297.64236237209519</v>
+        <v>294.61921041524977</v>
       </c>
       <c r="T74" s="38">
-        <v>301.28417987165824</v>
+        <v>298.21980357549205</v>
       </c>
       <c r="U74" s="38">
-        <v>304.3657177559038</v>
+        <v>301.26645932646625</v>
       </c>
     </row>
     <row r="75" spans="1:22">
-      <c r="B75" s="153"/>
+      <c r="B75" s="156"/>
       <c r="C75" s="37">
         <v>0.11</v>
       </c>
       <c r="D75" s="38">
-        <v>250.56106409055718</v>
+        <v>247.72799513115362</v>
       </c>
       <c r="E75" s="38">
-        <v>250.51151226277906</v>
+        <v>247.6790571442308</v>
       </c>
       <c r="F75" s="38">
-        <v>250.36546477038041</v>
+        <v>247.53481886698464</v>
       </c>
       <c r="G75" s="52">
-        <v>250.10683900259124</v>
+        <v>247.2793969176945</v>
       </c>
       <c r="H75" s="38">
-        <v>249.71576820493078</v>
+        <v>246.89317064835271</v>
       </c>
       <c r="I75" s="38">
-        <v>249.16741893429824</v>
+        <v>246.35161424894952</v>
       </c>
       <c r="J75" s="38">
-        <v>248.43033549609899</v>
-      </c>
-      <c r="M75" s="153"/>
+        <v>245.62366169347271</v>
+      </c>
+      <c r="M75" s="156"/>
       <c r="N75" s="37">
         <v>0.11</v>
       </c>
       <c r="O75" s="38">
-        <v>233.25921755803853</v>
+        <v>230.64048136393893</v>
       </c>
       <c r="P75" s="38">
-        <v>240.27905982660224</v>
+        <v>237.57336284467041</v>
       </c>
       <c r="Q75" s="38">
-        <v>245.7389371465961</v>
+        <v>242.96560399635047</v>
       </c>
       <c r="R75" s="52">
-        <v>250.10683900259124</v>
+        <v>247.2793969176945</v>
       </c>
       <c r="S75" s="38">
-        <v>253.68057688476912</v>
+        <v>250.8088638533396</v>
       </c>
       <c r="T75" s="38">
-        <v>256.65869178658403</v>
+        <v>253.75008629971055</v>
       </c>
       <c r="U75" s="38">
-        <v>259.17863516504269</v>
+        <v>256.23881298510133</v>
       </c>
     </row>
     <row r="76" spans="1:22">
-      <c r="B76" s="154"/>
+      <c r="B76" s="157"/>
       <c r="C76" s="37">
         <v>0.12</v>
       </c>
       <c r="D76" s="38">
-        <v>217.83693670761056</v>
+        <v>215.10443574188787</v>
       </c>
       <c r="E76" s="38">
-        <v>217.22160046353318</v>
+        <v>214.4973728632518</v>
       </c>
       <c r="F76" s="38">
-        <v>216.47162654553802</v>
+        <v>213.75748255134164</v>
       </c>
       <c r="G76" s="52">
-        <v>215.5668193025374</v>
+        <v>212.86484069116605</v>
       </c>
       <c r="H76" s="38">
-        <v>214.48273136742512</v>
+        <v>211.79532861720961</v>
       </c>
       <c r="I76" s="38">
-        <v>213.1894826248494</v>
+        <v>210.51946796050879</v>
       </c>
       <c r="J76" s="38">
-        <v>211.65016234408128</v>
-      </c>
-      <c r="M76" s="154"/>
+        <v>209.00084426528508</v>
+      </c>
+      <c r="M76" s="157"/>
       <c r="N76" s="37">
         <v>0.12</v>
       </c>
       <c r="O76" s="38">
-        <v>201.60693612481319</v>
+        <v>199.09265199131485</v>
       </c>
       <c r="P76" s="38">
-        <v>207.42355411553163</v>
+        <v>204.83106394958622</v>
       </c>
       <c r="Q76" s="38">
-        <v>211.94759033053484</v>
+        <v>209.29427325046393</v>
       </c>
       <c r="R76" s="52">
-        <v>215.5668193025374</v>
+        <v>212.86484069116605</v>
       </c>
       <c r="S76" s="38">
-        <v>218.52800664326671</v>
+        <v>215.78621405174059</v>
       </c>
       <c r="T76" s="38">
-        <v>220.99566276054122</v>
+        <v>218.2206918522194</v>
       </c>
       <c r="U76" s="38">
-        <v>223.08367947515811</v>
+        <v>220.28063460647061</v>
       </c>
     </row>
   </sheetData>
@@ -47593,7 +47664,7 @@
       <c r="E35" s="91"/>
       <c r="F35" s="98">
         <f>+Main!H4</f>
-        <v>34917.850457599998</v>
+        <v>31405.222593799997</v>
       </c>
       <c r="G35" s="91"/>
       <c r="H35" s="91"/>
@@ -47703,7 +47774,7 @@
       <c r="E37" s="91"/>
       <c r="F37" s="98">
         <f>F35+F36</f>
-        <v>47479.850457599998</v>
+        <v>43967.222593799997</v>
       </c>
       <c r="G37" s="91"/>
       <c r="H37" s="91"/>
@@ -47914,7 +47985,7 @@
       <c r="E41" s="123"/>
       <c r="F41" s="124">
         <f>+(F36/F37*F32*(1-F40))+(F35/F37*F22)</f>
-        <v>2.6284996548209517E-2</v>
+        <v>2.6571408971464185E-2</v>
       </c>
       <c r="G41" s="91"/>
       <c r="H41" s="119" t="s">
@@ -48061,23 +48132,23 @@
     <row r="3" spans="1:35">
       <c r="A3" s="92"/>
       <c r="B3" s="91"/>
-      <c r="C3" s="157" t="s">
+      <c r="C3" s="160" t="s">
         <v>117</v>
       </c>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157"/>
-      <c r="J3" s="157" t="s">
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="K3" s="157"/>
-      <c r="L3" s="157"/>
-      <c r="M3" s="157"/>
-      <c r="N3" s="157"/>
-      <c r="O3" s="157"/>
+      <c r="K3" s="160"/>
+      <c r="L3" s="160"/>
+      <c r="M3" s="160"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
       <c r="P3" s="91"/>
       <c r="Q3" s="91"/>
       <c r="R3" s="91"/>

--- a/KER.PA.xlsx
+++ b/KER.PA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6491B2-FE07-482D-99D2-3E98C136B354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D76769-9489-4E01-8D4B-4A68DA1C5BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3120" windowWidth="38175" windowHeight="15240" xr2:uid="{00BE0985-5336-41E3-B925-F565FA10FCAA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00BE0985-5336-41E3-B925-F565FA10FCAA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -7922,7 +7922,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="58">
-        <v>256.14999999999998</v>
+        <v>245.3</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="H4" s="62">
         <f>H3*H2</f>
-        <v>31405.222593799997</v>
+        <v>30074.960383599999</v>
       </c>
       <c r="K4" s="61"/>
       <c r="N4" s="62"/>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="H7" s="62">
         <f>H4+H6-H5</f>
-        <v>39654.222593799997</v>
+        <v>38323.960383600002</v>
       </c>
       <c r="N7" s="62"/>
     </row>
@@ -43408,14 +43408,14 @@
       </c>
       <c r="J3" s="14">
         <f>+Main!H2</f>
-        <v>256.14999999999998</v>
+        <v>245.3</v>
       </c>
       <c r="L3" t="s">
         <v>151</v>
       </c>
       <c r="O3" s="14">
         <f>+J3</f>
-        <v>256.14999999999998</v>
+        <v>245.3</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -43424,14 +43424,14 @@
       </c>
       <c r="E4" s="48">
         <f ca="1">+TODAY()</f>
-        <v>46143</v>
+        <v>46226</v>
       </c>
       <c r="G4" t="s">
         <v>152</v>
       </c>
       <c r="J4" s="56">
         <f ca="1">V62</f>
-        <v>345.59261421468523</v>
+        <v>339.64481512044307</v>
       </c>
       <c r="L4" t="s">
         <v>534</v>
@@ -43453,7 +43453,7 @@
       </c>
       <c r="J5" s="16">
         <f ca="1">J4/J3-1</f>
-        <v>0.34918061376023912</v>
+        <v>0.3846099271114678</v>
       </c>
       <c r="L5" t="s">
         <v>154</v>
@@ -45072,43 +45072,43 @@
       <c r="L52" s="44"/>
       <c r="M52" s="44">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>383.32884859296615</v>
+        <v>630.60476450894737</v>
       </c>
       <c r="N52" s="44">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>1376.0893233613535</v>
+        <v>1349.3409505802533</v>
       </c>
       <c r="O52" s="44">
         <f t="shared" ref="O52:U52" ca="1" si="23">O51/(1+$E$18)^O53</f>
-        <v>1743.2171241317808</v>
+        <v>1709.3325348953954</v>
       </c>
       <c r="P52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2088.5661362941655</v>
+        <v>2047.9686658806049</v>
       </c>
       <c r="Q52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2624.5977202580189</v>
+        <v>2573.5808879709966</v>
       </c>
       <c r="R52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2740.5692302548896</v>
+        <v>2687.2981480956232</v>
       </c>
       <c r="S52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2840.6758503740953</v>
+        <v>2785.4588994784417</v>
       </c>
       <c r="T52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2797.6064984488967</v>
+        <v>2743.2267280045253</v>
       </c>
       <c r="U52" s="44">
         <f t="shared" ca="1" si="23"/>
-        <v>2601.0778185824533</v>
+        <v>2550.5181652642036</v>
       </c>
       <c r="V52" s="45">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>2415.3589046372144</v>
+        <v>2368.4092486195568</v>
       </c>
     </row>
     <row r="53" spans="2:24">
@@ -45117,43 +45117,43 @@
       </c>
       <c r="M53" s="53">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.33611111111111114</v>
+        <v>0.56388888888888888</v>
       </c>
       <c r="N53" s="53">
         <f ca="1">M53+1</f>
-        <v>1.3361111111111112</v>
+        <v>1.5638888888888889</v>
       </c>
       <c r="O53" s="53">
         <f ca="1">N53+1</f>
-        <v>2.3361111111111112</v>
+        <v>2.5638888888888891</v>
       </c>
       <c r="P53" s="53">
         <f t="shared" ref="P53:V53" ca="1" si="24">O53+1</f>
-        <v>3.3361111111111112</v>
+        <v>3.5638888888888891</v>
       </c>
       <c r="Q53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>4.3361111111111112</v>
+        <v>4.5638888888888891</v>
       </c>
       <c r="R53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>5.3361111111111112</v>
+        <v>5.5638888888888891</v>
       </c>
       <c r="S53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>6.3361111111111112</v>
+        <v>6.5638888888888891</v>
       </c>
       <c r="T53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>7.3361111111111112</v>
+        <v>7.5638888888888891</v>
       </c>
       <c r="U53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>8.3361111111111121</v>
+        <v>8.56388888888889</v>
       </c>
       <c r="V53" s="53">
         <f t="shared" ca="1" si="24"/>
-        <v>9.3361111111111121</v>
+        <v>9.56388888888889</v>
       </c>
     </row>
     <row r="54" spans="2:24">
@@ -45166,7 +45166,7 @@
       <c r="Q54" s="4"/>
       <c r="V54" s="8">
         <f ca="1">SUM(M52:V52)</f>
-        <v>21611.087454935834</v>
+        <v>21445.738993298546</v>
       </c>
     </row>
     <row r="55" spans="2:24">
@@ -45208,7 +45208,7 @@
       <c r="U56" s="9"/>
       <c r="V56" s="50">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>29009.230039444174</v>
+        <v>28445.349711318126</v>
       </c>
     </row>
     <row r="57" spans="2:24">
@@ -45236,7 +45236,7 @@
       <c r="U57" s="34"/>
       <c r="V57" s="55">
         <f ca="1">V54+V56</f>
-        <v>50620.317494380011</v>
+        <v>49891.088704616675</v>
       </c>
     </row>
     <row r="58" spans="2:24">
@@ -45290,7 +45290,7 @@
       <c r="Q60" s="4"/>
       <c r="V60" s="46">
         <f ca="1">V57+V58-V59</f>
-        <v>42371.317494380011</v>
+        <v>41642.088704616675</v>
       </c>
     </row>
     <row r="61" spans="2:24">
@@ -45327,7 +45327,7 @@
       </c>
       <c r="V62" s="46">
         <f ca="1">V60/V61</f>
-        <v>345.59261421468523</v>
+        <v>339.64481512044307</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -45388,7 +45388,7 @@
       </c>
       <c r="C69" s="36">
         <f ca="1">+J4</f>
-        <v>345.59261421468523</v>
+        <v>339.64481512044307</v>
       </c>
       <c r="D69" s="51">
         <v>5.0000000000000001E-3</v>
@@ -45416,7 +45416,7 @@
       </c>
       <c r="N69" s="36">
         <f ca="1">+J4</f>
-        <v>345.59261421468523</v>
+        <v>339.64481512044307</v>
       </c>
       <c r="O69" s="51">
         <v>7.0000000000000007E-2</v>
@@ -45447,25 +45447,25 @@
       </c>
       <c r="D70" s="38">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>596.70941523707836</v>
+        <v>590.065498023744</v>
       </c>
       <c r="E70" s="38">
-        <v>618.33118338367001</v>
+        <v>611.40219022804308</v>
       </c>
       <c r="F70" s="38">
-        <v>644.46513545749406</v>
+        <v>637.19157469006177</v>
       </c>
       <c r="G70" s="52">
-        <v>676.803340431263</v>
+        <v>669.10341100644587</v>
       </c>
       <c r="H70" s="38">
-        <v>718.00476383352429</v>
+        <v>709.76160711477974</v>
       </c>
       <c r="I70" s="38">
-        <v>772.50101487852476</v>
+        <v>763.53934291103906</v>
       </c>
       <c r="J70" s="38">
-        <v>848.26899015190713</v>
+        <v>838.30834220797851</v>
       </c>
       <c r="M70" s="156"/>
       <c r="N70" s="37">
@@ -45473,25 +45473,25 @@
       </c>
       <c r="O70" s="38">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>619.23422828015805</v>
+        <v>612.29332877288323</v>
       </c>
       <c r="P70" s="38">
-        <v>643.22135834311837</v>
+        <v>635.96419637020085</v>
       </c>
       <c r="Q70" s="38">
-        <v>661.87801505875439</v>
+        <v>654.37487116811496</v>
       </c>
       <c r="R70" s="52">
-        <v>676.803340431263</v>
+        <v>669.10341100644587</v>
       </c>
       <c r="S70" s="38">
-        <v>689.01497028149743</v>
+        <v>681.15403451053498</v>
       </c>
       <c r="T70" s="38">
-        <v>699.19132849002608</v>
+        <v>691.19622076394239</v>
       </c>
       <c r="U70" s="38">
-        <v>707.80209312801196</v>
+        <v>699.69345528605663</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -45500,50 +45500,50 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D71" s="38">
-        <v>482.98202668795193</v>
+        <v>476.66629154548696</v>
       </c>
       <c r="E71" s="38">
-        <v>494.1181029265378</v>
+        <v>487.63206385122334</v>
       </c>
       <c r="F71" s="38">
-        <v>507.05957334319748</v>
+        <v>500.37562045501079</v>
       </c>
       <c r="G71" s="52">
-        <v>522.34805619135307</v>
+        <v>515.43029664626499</v>
       </c>
       <c r="H71" s="38">
-        <v>540.76588894816973</v>
+        <v>533.56646562080778</v>
       </c>
       <c r="I71" s="38">
-        <v>563.48657782939563</v>
+        <v>555.9396871723726</v>
       </c>
       <c r="J71" s="38">
-        <v>592.35420403120611</v>
+        <v>584.36584097682601</v>
       </c>
       <c r="M71" s="156"/>
       <c r="N71" s="37">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O71" s="38">
-        <v>480.1582359274534</v>
+        <v>473.88568499653246</v>
       </c>
       <c r="P71" s="38">
-        <v>497.73732770407815</v>
+        <v>491.19593985058765</v>
       </c>
       <c r="Q71" s="38">
-        <v>511.40995464145311</v>
+        <v>504.6594714037418</v>
       </c>
       <c r="R71" s="52">
-        <v>522.34805619135307</v>
+        <v>515.43029664626499</v>
       </c>
       <c r="S71" s="38">
-        <v>531.29741200490753</v>
+        <v>524.24279002651133</v>
       </c>
       <c r="T71" s="38">
-        <v>538.75520851620297</v>
+        <v>531.58653451004989</v>
       </c>
       <c r="U71" s="38">
-        <v>545.06565171806812</v>
+        <v>537.80047214996705</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -45552,50 +45552,50 @@
         <v>0.08</v>
       </c>
       <c r="D72" s="52">
-        <v>400.03034784046696</v>
+        <v>393.99820701233728</v>
       </c>
       <c r="E72" s="52">
-        <v>405.68702778144677</v>
+        <v>399.55658936584706</v>
       </c>
       <c r="F72" s="52">
-        <v>412.04380390764453</v>
+        <v>405.8029021524514</v>
       </c>
       <c r="G72" s="52">
-        <v>419.27570026536478</v>
+        <v>412.90912798042382</v>
       </c>
       <c r="H72" s="52">
-        <v>427.62138600865893</v>
+        <v>421.10978858831919</v>
       </c>
       <c r="I72" s="52">
-        <v>437.41499795319947</v>
+        <v>430.73321441011456</v>
       </c>
       <c r="J72" s="52">
-        <v>449.13917816606823</v>
+        <v>442.25366051710984</v>
       </c>
       <c r="M72" s="156"/>
       <c r="N72" s="37">
         <v>0.08</v>
       </c>
       <c r="O72" s="52">
-        <v>387.04210507095462</v>
+        <v>381.23566429003256</v>
       </c>
       <c r="P72" s="52">
-        <v>400.47276973529227</v>
+        <v>394.43294082769557</v>
       </c>
       <c r="Q72" s="52">
-        <v>410.91884225199925</v>
+        <v>404.69748924587793</v>
       </c>
       <c r="R72" s="52">
-        <v>419.27570026536478</v>
+        <v>412.90912798042382</v>
       </c>
       <c r="S72" s="52">
-        <v>426.11312954902752</v>
+        <v>419.62774149050676</v>
       </c>
       <c r="T72" s="52">
-        <v>431.81098728541326</v>
+        <v>425.22658608224265</v>
       </c>
       <c r="U72" s="52">
-        <v>436.63225152389339</v>
+        <v>429.96406996755758</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -45604,50 +45604,50 @@
         <v>0.09</v>
       </c>
       <c r="D73" s="38">
-        <v>336.97055966878679</v>
+        <v>331.19035574821345</v>
       </c>
       <c r="E73" s="38">
-        <v>339.61218320547522</v>
+        <v>333.78063150543215</v>
       </c>
       <c r="F73" s="38">
-        <v>342.4707084110895</v>
+        <v>336.58359280505147</v>
       </c>
       <c r="G73" s="52">
-        <v>345.59261421468523</v>
+        <v>339.64481512044307</v>
       </c>
       <c r="H73" s="38">
-        <v>349.03868075425788</v>
+        <v>343.02389714755407</v>
       </c>
       <c r="I73" s="38">
-        <v>352.88994821380197</v>
+        <v>346.80030381431476</v>
       </c>
       <c r="J73" s="38">
-        <v>357.2569259351277</v>
+        <v>351.08239638608399</v>
       </c>
       <c r="M73" s="156"/>
       <c r="N73" s="37">
         <v>0.09</v>
       </c>
       <c r="O73" s="38">
-        <v>320.24180017044978</v>
+        <v>314.78676925109841</v>
       </c>
       <c r="P73" s="38">
-        <v>330.80463935554792</v>
+        <v>325.14428836332536</v>
       </c>
       <c r="Q73" s="38">
-        <v>339.02018094395754</v>
+        <v>333.20013656172404</v>
       </c>
       <c r="R73" s="52">
-        <v>345.59261421468523</v>
+        <v>339.64481512044307</v>
       </c>
       <c r="S73" s="38">
-        <v>350.97005961800784</v>
+        <v>344.91773394121304</v>
       </c>
       <c r="T73" s="38">
-        <v>355.45126412077678</v>
+        <v>349.31183295852151</v>
       </c>
       <c r="U73" s="38">
-        <v>359.24305254619657</v>
+        <v>353.02991674239775</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -45656,50 +45656,50 @@
         <v>0.1</v>
       </c>
       <c r="D74" s="38">
-        <v>287.50274393382966</v>
+        <v>281.95050617932748</v>
       </c>
       <c r="E74" s="38">
-        <v>288.43466216353943</v>
+        <v>282.8624109199236</v>
       </c>
       <c r="F74" s="38">
-        <v>289.36658039324919</v>
+        <v>283.77431566051979</v>
       </c>
       <c r="G74" s="52">
-        <v>290.29849862295896</v>
+        <v>284.68622040111592</v>
       </c>
       <c r="H74" s="38">
-        <v>291.23041685266867</v>
+        <v>285.59812514171199</v>
       </c>
       <c r="I74" s="38">
-        <v>292.16233508237849</v>
+        <v>286.51002988230812</v>
       </c>
       <c r="J74" s="38">
-        <v>293.0942533120882</v>
+        <v>287.42193462290425</v>
       </c>
       <c r="M74" s="156"/>
       <c r="N74" s="37">
         <v>0.1</v>
       </c>
       <c r="O74" s="38">
-        <v>269.92942874501676</v>
+        <v>264.75458821380056</v>
       </c>
       <c r="P74" s="38">
-        <v>278.41654119415938</v>
+        <v>273.05943495851534</v>
       </c>
       <c r="Q74" s="38">
-        <v>285.01762865460358</v>
+        <v>279.51876020440449</v>
       </c>
       <c r="R74" s="52">
-        <v>290.29849862295896</v>
+        <v>284.68622040111592</v>
       </c>
       <c r="S74" s="38">
-        <v>294.61921041524977</v>
+        <v>288.91414238024345</v>
       </c>
       <c r="T74" s="38">
-        <v>298.21980357549205</v>
+        <v>292.43741069618301</v>
       </c>
       <c r="U74" s="38">
-        <v>301.26645932646625</v>
+        <v>295.41863773274724</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -45708,50 +45708,50 @@
         <v>0.11</v>
       </c>
       <c r="D75" s="38">
-        <v>247.72799513115362</v>
+        <v>242.38467718497333</v>
       </c>
       <c r="E75" s="38">
-        <v>247.6790571442308</v>
+        <v>242.33688878024267</v>
       </c>
       <c r="F75" s="38">
-        <v>247.53481886698464</v>
+        <v>242.19603874524711</v>
       </c>
       <c r="G75" s="52">
-        <v>247.2793969176945</v>
+        <v>241.94661680827582</v>
       </c>
       <c r="H75" s="38">
-        <v>246.89317064835271</v>
+        <v>241.56946322192121</v>
       </c>
       <c r="I75" s="38">
-        <v>246.35161424894952</v>
+        <v>241.04062830192407</v>
       </c>
       <c r="J75" s="38">
-        <v>245.62366169347271</v>
+        <v>240.32977578155572</v>
       </c>
       <c r="M75" s="156"/>
       <c r="N75" s="37">
         <v>0.11</v>
       </c>
       <c r="O75" s="38">
-        <v>230.64048136393893</v>
+        <v>225.69855919985795</v>
       </c>
       <c r="P75" s="38">
-        <v>237.57336284467041</v>
+        <v>232.46858320336537</v>
       </c>
       <c r="Q75" s="38">
-        <v>242.96560399635047</v>
+        <v>237.73415742831563</v>
       </c>
       <c r="R75" s="52">
-        <v>247.2793969176945</v>
+        <v>241.94661680827582</v>
       </c>
       <c r="S75" s="38">
-        <v>250.8088638533396</v>
+        <v>245.39317448278865</v>
       </c>
       <c r="T75" s="38">
-        <v>253.75008629971055</v>
+        <v>248.26530587821608</v>
       </c>
       <c r="U75" s="38">
-        <v>256.23881298510133</v>
+        <v>250.69557090511623</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -45760,50 +45760,50 @@
         <v>0.12</v>
       </c>
       <c r="D76" s="38">
-        <v>215.10443574188787</v>
+        <v>209.95434139909997</v>
       </c>
       <c r="E76" s="38">
-        <v>214.4973728632518</v>
+        <v>209.36274856454753</v>
       </c>
       <c r="F76" s="38">
-        <v>213.75748255134164</v>
+        <v>208.64171319525536</v>
       </c>
       <c r="G76" s="52">
-        <v>212.86484069116605</v>
+        <v>207.77181891101262</v>
       </c>
       <c r="H76" s="38">
-        <v>211.79532861720961</v>
+        <v>206.72956167261648</v>
       </c>
       <c r="I76" s="38">
-        <v>210.51946796050879</v>
+        <v>205.48621432104147</v>
       </c>
       <c r="J76" s="38">
-        <v>209.00084426528508</v>
+        <v>204.0062903657265</v>
       </c>
       <c r="M76" s="157"/>
       <c r="N76" s="37">
         <v>0.12</v>
       </c>
       <c r="O76" s="38">
-        <v>199.09265199131485</v>
+        <v>194.35059281126726</v>
       </c>
       <c r="P76" s="38">
-        <v>204.83106394958622</v>
+        <v>199.94277035282781</v>
       </c>
       <c r="Q76" s="38">
-        <v>209.29427325046393</v>
+        <v>204.29224177404166</v>
       </c>
       <c r="R76" s="52">
-        <v>212.86484069116605</v>
+        <v>207.77181891101262</v>
       </c>
       <c r="S76" s="38">
-        <v>215.78621405174059</v>
+        <v>210.61874565944345</v>
       </c>
       <c r="T76" s="38">
-        <v>218.2206918522194</v>
+        <v>212.99118461646918</v>
       </c>
       <c r="U76" s="38">
-        <v>220.28063460647061</v>
+        <v>214.99863296472171</v>
       </c>
     </row>
   </sheetData>
@@ -47664,7 +47664,7 @@
       <c r="E35" s="91"/>
       <c r="F35" s="98">
         <f>+Main!H4</f>
-        <v>31405.222593799997</v>
+        <v>30074.960383599999</v>
       </c>
       <c r="G35" s="91"/>
       <c r="H35" s="91"/>
@@ -47774,7 +47774,7 @@
       <c r="E37" s="91"/>
       <c r="F37" s="98">
         <f>F35+F36</f>
-        <v>43967.222593799997</v>
+        <v>42636.960383600002</v>
       </c>
       <c r="G37" s="91"/>
       <c r="H37" s="91"/>
@@ -47985,7 +47985,7 @@
       <c r="E41" s="123"/>
       <c r="F41" s="124">
         <f>+(F36/F37*F32*(1-F40))+(F35/F37*F22)</f>
-        <v>2.6571408971464185E-2</v>
+        <v>2.6692195936778643E-2</v>
       </c>
       <c r="G41" s="91"/>
       <c r="H41" s="119" t="s">
